--- a/docs/all/idx11_pobreza_loadings_y_tops.xlsx
+++ b/docs/all/idx11_pobreza_loadings_y_tops.xlsx
@@ -399,7 +399,7 @@
         <v>0.2442883463929779</v>
       </c>
       <c r="D2">
-        <v>0.05160223631492519</v>
+        <v>0.05160223631492518</v>
       </c>
       <c r="E2">
         <v>5.2</v>
@@ -420,7 +420,7 @@
         <v>0.2268627822099163</v>
       </c>
       <c r="D3">
-        <v>0.04792134815889038</v>
+        <v>0.04792134815889036</v>
       </c>
       <c r="E3">
         <v>4.8</v>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.157695016321636</v>
+        <v>0.1576950163216361</v>
       </c>
       <c r="D5">
         <v>0.03331069868074951</v>
@@ -504,7 +504,7 @@
         <v>0.1145427871481473</v>
       </c>
       <c r="D7">
-        <v>0.02419543976559815</v>
+        <v>0.02419543976559814</v>
       </c>
       <c r="E7">
         <v>2.4</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.2351261304289207</v>
+        <v>0.2351261304289208</v>
       </c>
       <c r="D8">
-        <v>0.04966685609590688</v>
+        <v>0.0496668560959069</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.2213377954888254</v>
+        <v>0.2213377954888255</v>
       </c>
       <c r="D9">
-        <v>0.04675427787236952</v>
+        <v>0.04675427787236953</v>
       </c>
       <c r="E9">
         <v>4.7</v>
@@ -567,7 +567,7 @@
         <v>0.1840816992443776</v>
       </c>
       <c r="D10">
-        <v>0.03888448829393037</v>
+        <v>0.03888448829393035</v>
       </c>
       <c r="E10">
         <v>3.9</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.2098674752857456</v>
+        <v>0.2098674752857458</v>
       </c>
       <c r="D11">
-        <v>0.0443313453728592</v>
+        <v>0.04433134537285922</v>
       </c>
       <c r="E11">
         <v>4.4</v>
@@ -609,7 +609,7 @@
         <v>0.2031859421367442</v>
       </c>
       <c r="D12">
-        <v>0.04291997206098562</v>
+        <v>0.04291997206098561</v>
       </c>
       <c r="E12">
         <v>4.3</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.2032805507865643</v>
+        <v>0.2032805507865645</v>
       </c>
       <c r="D13">
-        <v>0.04293995671427563</v>
+        <v>0.04293995671427565</v>
       </c>
       <c r="E13">
         <v>4.3</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.2003759995384211</v>
+        <v>0.2003759995384212</v>
       </c>
       <c r="D14">
-        <v>0.04232641398041804</v>
+        <v>0.04232641398041805</v>
       </c>
       <c r="E14">
         <v>4.2</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.20965304680222</v>
+        <v>0.2096530468022201</v>
       </c>
       <c r="D15">
-        <v>0.04428605058314483</v>
+        <v>0.04428605058314485</v>
       </c>
       <c r="E15">
         <v>4.4</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.1930811761962004</v>
+        <v>0.1930811761962006</v>
       </c>
       <c r="D16">
-        <v>0.04078549234605013</v>
+        <v>0.04078549234605015</v>
       </c>
       <c r="E16">
         <v>4.1</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.2005370670276991</v>
+        <v>0.2005370670276992</v>
       </c>
       <c r="D17">
-        <v>0.04236043706325066</v>
+        <v>0.04236043706325069</v>
       </c>
       <c r="E17">
         <v>4.2</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.2268976465295912</v>
+        <v>0.2268976465295914</v>
       </c>
       <c r="D18">
-        <v>0.04792871272166788</v>
+        <v>0.0479287127216679</v>
       </c>
       <c r="E18">
         <v>4.8</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.219754456166576</v>
+        <v>0.2197544561665761</v>
       </c>
       <c r="D20">
-        <v>0.04641982127188154</v>
+        <v>0.04641982127188155</v>
       </c>
       <c r="E20">
         <v>4.6</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.2327915016788113</v>
+        <v>0.2327915016788114</v>
       </c>
       <c r="D22">
         <v>0.04917370091167651</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.2305650063878259</v>
+        <v>0.230565006387826</v>
       </c>
       <c r="D23">
-        <v>0.04870338729313543</v>
+        <v>0.04870338729313544</v>
       </c>
       <c r="E23">
         <v>4.9</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.2348736677440059</v>
+        <v>0.234873667744006</v>
       </c>
       <c r="D24">
-        <v>0.04961352715361376</v>
+        <v>0.04961352715361377</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.2217901836143532</v>
+        <v>0.2217901836143535</v>
       </c>
       <c r="D25">
-        <v>0.05335907280647808</v>
+        <v>0.05335907280647813</v>
       </c>
       <c r="E25">
         <v>5.3</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.2936727925108271</v>
+        <v>0.2936727925108273</v>
       </c>
       <c r="D26">
-        <v>0.07065284703543957</v>
+        <v>0.0706528470354396</v>
       </c>
       <c r="E26">
         <v>7.1</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.3182170713975063</v>
+        <v>0.3182170713975068</v>
       </c>
       <c r="D27">
-        <v>0.07655779712274391</v>
+        <v>0.07655779712274398</v>
       </c>
       <c r="E27">
         <v>7.7</v>
@@ -945,7 +945,7 @@
         <v>0.310517022537159</v>
       </c>
       <c r="D28">
-        <v>0.07470529192590832</v>
+        <v>0.07470529192590826</v>
       </c>
       <c r="E28">
         <v>7.5</v>
@@ -966,7 +966,7 @@
         <v>0.3884652032738328</v>
       </c>
       <c r="D29">
-        <v>0.09345834304512621</v>
+        <v>0.09345834304512615</v>
       </c>
       <c r="E29">
         <v>9.300000000000001</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.3935018668737267</v>
+        <v>0.3935018668737266</v>
       </c>
       <c r="D30">
-        <v>0.09467008152402921</v>
+        <v>0.09467008152402914</v>
       </c>
       <c r="E30">
         <v>9.5</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.113994269463961</v>
+        <v>0.1139942694639613</v>
       </c>
       <c r="D31">
-        <v>0.02742514760899064</v>
+        <v>0.02742514760899071</v>
       </c>
       <c r="E31">
         <v>2.7</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.1303513235528818</v>
+        <v>0.1303513235528821</v>
       </c>
       <c r="D32">
-        <v>0.03136038597620276</v>
+        <v>0.03136038597620282</v>
       </c>
       <c r="E32">
         <v>3.1</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.09445823571526259</v>
+        <v>0.09445823571526281</v>
       </c>
       <c r="D33">
-        <v>0.02272509898574242</v>
+        <v>0.02272509898574247</v>
       </c>
       <c r="E33">
         <v>2.3</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.1306557309427679</v>
+        <v>-0.1306557309427678</v>
       </c>
       <c r="D34">
-        <v>0.03143362139093151</v>
+        <v>0.03143362139093148</v>
       </c>
       <c r="E34">
         <v>3.1</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.1514298437247672</v>
+        <v>-0.151429843724767</v>
       </c>
       <c r="D35">
-        <v>0.03643153148037044</v>
+        <v>0.03643153148037038</v>
       </c>
       <c r="E35">
         <v>3.6</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.111000212117288</v>
+        <v>-0.1110002121172881</v>
       </c>
       <c r="D36">
-        <v>0.02670482662208131</v>
+        <v>0.02670482662208132</v>
       </c>
       <c r="E36">
         <v>2.7</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.2370396140579388</v>
+        <v>-0.2370396140579389</v>
       </c>
       <c r="D37">
-        <v>0.05702783512966302</v>
+        <v>0.05702783512966301</v>
       </c>
       <c r="E37">
         <v>5.7</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.2077647244895507</v>
+        <v>-0.207764724489551</v>
       </c>
       <c r="D38">
-        <v>0.04998477786524703</v>
+        <v>0.04998477786524706</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.2359955206627522</v>
+        <v>-0.2359955206627527</v>
       </c>
       <c r="D39">
-        <v>0.05677664341963044</v>
+        <v>0.05677664341963054</v>
       </c>
       <c r="E39">
         <v>5.7</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.2285038719485794</v>
+        <v>-0.2285038719485796</v>
       </c>
       <c r="D40">
-        <v>0.05497427587267362</v>
+        <v>0.05497427587267365</v>
       </c>
       <c r="E40">
         <v>5.5</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.03384734391602286</v>
+        <v>-0.03384734391602291</v>
       </c>
       <c r="D41">
-        <v>0.008143114627026651</v>
+        <v>0.008143114627026661</v>
       </c>
       <c r="E41">
         <v>0.8</v>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C42">
-        <v>-0.04104191297386503</v>
+        <v>-0.04104191297386497</v>
       </c>
       <c r="D42">
-        <v>0.009874009691508626</v>
+        <v>0.009874009691508609</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.0288092247933496</v>
+        <v>-0.02880922479334963</v>
       </c>
       <c r="D43">
-        <v>0.006931025973266077</v>
+        <v>0.006931025973266083</v>
       </c>
       <c r="E43">
         <v>0.7</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.1266535931533375</v>
+        <v>-0.1266535931533374</v>
       </c>
       <c r="D45">
-        <v>0.03047077281843071</v>
+        <v>0.03047077281843068</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.1167745530047196</v>
+        <v>-0.1167745530047195</v>
       </c>
       <c r="D46">
-        <v>0.02809403813180995</v>
+        <v>0.02809403813180991</v>
       </c>
       <c r="E46">
         <v>2.8</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.122125830837832</v>
+        <v>-0.1221258308378318</v>
       </c>
       <c r="D47">
-        <v>0.02938146762418652</v>
+        <v>0.02938146762418647</v>
       </c>
       <c r="E47">
         <v>2.9</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.04958060309528725</v>
+        <v>-0.04958060309528575</v>
       </c>
       <c r="D48">
-        <v>0.01259378638351679</v>
+        <v>0.01259378638351646</v>
       </c>
       <c r="E48">
         <v>1.3</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.04867225650852022</v>
+        <v>-0.04867225650851836</v>
       </c>
       <c r="D49">
-        <v>0.01236306061251406</v>
+        <v>0.01236306061251364</v>
       </c>
       <c r="E49">
         <v>1.2</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.08238988524939198</v>
+        <v>-0.08238988524938917</v>
       </c>
       <c r="D50">
-        <v>0.02092755130467401</v>
+        <v>0.0209275513046734</v>
       </c>
       <c r="E50">
         <v>2.1</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.05169344932851228</v>
+        <v>-0.05169344932852148</v>
       </c>
       <c r="D51">
-        <v>0.01313046267346259</v>
+        <v>0.01313046267346499</v>
       </c>
       <c r="E51">
         <v>1.3</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.06085329651410306</v>
+        <v>-0.06085329651411248</v>
       </c>
       <c r="D52">
-        <v>0.01545712172073732</v>
+        <v>0.01545712172073979</v>
       </c>
       <c r="E52">
         <v>1.5</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>-0.1116673922422783</v>
+        <v>-0.1116673922422849</v>
       </c>
       <c r="D53">
-        <v>0.02836422302489714</v>
+        <v>0.02836422302489893</v>
       </c>
       <c r="E53">
         <v>2.8</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.03601775140124585</v>
+        <v>-0.03601775140123845</v>
       </c>
       <c r="D54">
-        <v>0.009148736377614139</v>
+        <v>0.0091487363776123</v>
       </c>
       <c r="E54">
         <v>0.9</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.02398859395791921</v>
+        <v>-0.0239885939579104</v>
       </c>
       <c r="D55">
-        <v>0.006093254399635812</v>
+        <v>0.006093254399633602</v>
       </c>
       <c r="E55">
         <v>0.6</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.01561502880752111</v>
+        <v>-0.01561502880751097</v>
       </c>
       <c r="D56">
-        <v>0.003966315956190417</v>
+        <v>0.003966315956187859</v>
       </c>
       <c r="E56">
         <v>0.4</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.3387036424553598</v>
+        <v>0.3387036424553563</v>
       </c>
       <c r="D57">
-        <v>0.08603286475164519</v>
+        <v>0.08603286475164471</v>
       </c>
       <c r="E57">
         <v>8.6</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.3192935743171782</v>
+        <v>0.3192935743171757</v>
       </c>
       <c r="D58">
-        <v>0.08110258483246043</v>
+        <v>0.08110258483246016</v>
       </c>
       <c r="E58">
         <v>8.1</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.3360340779154265</v>
+        <v>0.3360340779154224</v>
       </c>
       <c r="D59">
-        <v>0.08535477849504362</v>
+        <v>0.08535477849504298</v>
       </c>
       <c r="E59">
         <v>8.5</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>-0.2819419758435475</v>
+        <v>-0.2819419758435529</v>
       </c>
       <c r="D60">
-        <v>0.07161504287263887</v>
+        <v>0.07161504287264056</v>
       </c>
       <c r="E60">
         <v>7.2</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.2734768824213434</v>
+        <v>-0.2734768824213484</v>
       </c>
       <c r="D61">
-        <v>0.06946485566997684</v>
+        <v>0.06946485566997844</v>
       </c>
       <c r="E61">
         <v>6.9</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.2897352254960111</v>
+        <v>-0.2897352254960168</v>
       </c>
       <c r="D62">
-        <v>0.07359457751379515</v>
+        <v>0.07359457751379697</v>
       </c>
       <c r="E62">
         <v>7.4</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>-0.2656218676514341</v>
+        <v>-0.2656218676514399</v>
       </c>
       <c r="D63">
-        <v>0.06746963229882325</v>
+        <v>0.06746963229882502</v>
       </c>
       <c r="E63">
         <v>6.7</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.3107150718207169</v>
+        <v>0.310715071820715</v>
       </c>
       <c r="D64">
-        <v>0.07892359100853964</v>
+        <v>0.07892359100853952</v>
       </c>
       <c r="E64">
         <v>7.9</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.2955118710842665</v>
+        <v>0.2955118710842655</v>
       </c>
       <c r="D65">
-        <v>0.07506188198389123</v>
+        <v>0.07506188198389131</v>
       </c>
       <c r="E65">
         <v>7.5</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.3105882117213838</v>
+        <v>0.3105882117213811</v>
       </c>
       <c r="D66">
-        <v>0.07889136774194236</v>
+        <v>0.07889136774194204</v>
       </c>
       <c r="E66">
         <v>7.9</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.1079604306130016</v>
+        <v>-0.1079604306129971</v>
       </c>
       <c r="D67">
-        <v>0.02742263135443516</v>
+        <v>0.02742263135443413</v>
       </c>
       <c r="E67">
         <v>2.7</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>-0.1076156104015544</v>
+        <v>-0.1076156104015501</v>
       </c>
       <c r="D68">
-        <v>0.02733504484252162</v>
+        <v>0.02733504484252065</v>
       </c>
       <c r="E68">
         <v>2.7</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.1365334259096247</v>
+        <v>-0.1365334259096205</v>
       </c>
       <c r="D69">
-        <v>0.0346803526534547</v>
+        <v>0.0346803526534538</v>
       </c>
       <c r="E69">
         <v>3.5</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.08269983904844178</v>
+        <v>-0.08269983904843707</v>
       </c>
       <c r="D70">
-        <v>0.02100628152758983</v>
+        <v>0.02100628152758873</v>
       </c>
       <c r="E70">
         <v>2.1</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.05846447368577465</v>
+        <v>0.05846447368577599</v>
       </c>
       <c r="D71">
-        <v>0.01381965500421024</v>
+        <v>0.01381965500421045</v>
       </c>
       <c r="E71">
         <v>1.4</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.06579126733319043</v>
+        <v>0.06579126733319172</v>
       </c>
       <c r="D72">
-        <v>0.01555154026907258</v>
+        <v>0.01555154026907277</v>
       </c>
       <c r="E72">
         <v>1.6</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="C73">
-        <v>0.1079956546199421</v>
+        <v>0.107995654619944</v>
       </c>
       <c r="D73">
-        <v>0.02552768535680129</v>
+        <v>0.02552768535680154</v>
       </c>
       <c r="E73">
         <v>2.6</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C74">
-        <v>-0.3409430656374228</v>
+        <v>-0.3409430656374215</v>
       </c>
       <c r="D74">
-        <v>0.08059108799149979</v>
+        <v>0.08059108799149889</v>
       </c>
       <c r="E74">
         <v>8.1</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.3503344672158393</v>
+        <v>-0.3503344672158381</v>
       </c>
       <c r="D75">
-        <v>0.08281099901844692</v>
+        <v>0.082810999018446</v>
       </c>
       <c r="E75">
         <v>8.300000000000001</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>-0.2510863012052092</v>
+        <v>-0.2510863012052069</v>
       </c>
       <c r="D76">
-        <v>0.05935101849353511</v>
+        <v>0.05935101849353411</v>
       </c>
       <c r="E76">
         <v>5.9</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.2813782432761081</v>
+        <v>0.2813782432761093</v>
       </c>
       <c r="D77">
-        <v>0.06651133590402439</v>
+        <v>0.06651133590402418</v>
       </c>
       <c r="E77">
         <v>6.7</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.3246981623307877</v>
+        <v>0.3246981623307886</v>
       </c>
       <c r="D78">
-        <v>0.07675116700835624</v>
+        <v>0.07675116700835585</v>
       </c>
       <c r="E78">
         <v>7.7</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.3795756162507495</v>
+        <v>0.3795756162507498</v>
       </c>
       <c r="D79">
-        <v>0.0897229331574774</v>
+        <v>0.08972293315747679</v>
       </c>
       <c r="E79">
         <v>9</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>-0.1309315261449753</v>
+        <v>-0.130931526144984</v>
       </c>
       <c r="D80">
-        <v>0.03094919711795087</v>
+        <v>0.03094919711795269</v>
       </c>
       <c r="E80">
         <v>3.1</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.08664656345234839</v>
+        <v>-0.08664656345235651</v>
       </c>
       <c r="D81">
-        <v>0.02048125192484576</v>
+        <v>0.02048125192484752</v>
       </c>
       <c r="E81">
         <v>2</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.1679030030434307</v>
+        <v>-0.1679030030434393</v>
       </c>
       <c r="D82">
-        <v>0.03968840271618925</v>
+        <v>0.03968840271619099</v>
       </c>
       <c r="E82">
         <v>4</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.2125567370099262</v>
+        <v>-0.2125567370099182</v>
       </c>
       <c r="D83">
-        <v>0.05024351694476226</v>
+        <v>0.05024351694475999</v>
       </c>
       <c r="E83">
         <v>5</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="C84">
-        <v>-0.1973509082847366</v>
+        <v>-0.1973509082847291</v>
       </c>
       <c r="D84">
-        <v>0.04664920926032721</v>
+        <v>0.0466492092603251</v>
       </c>
       <c r="E84">
         <v>4.7</v>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="C85">
-        <v>-0.2087957368288925</v>
+        <v>-0.2087957368288848</v>
       </c>
       <c r="D85">
-        <v>0.04935450312669545</v>
+        <v>0.04935450312669324</v>
       </c>
       <c r="E85">
         <v>4.9</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C86">
-        <v>-0.2124337337540609</v>
+        <v>-0.2124337337540537</v>
       </c>
       <c r="D86">
-        <v>0.05021444180813161</v>
+        <v>0.05021444180812952</v>
       </c>
       <c r="E86">
         <v>5</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.06315954518422849</v>
+        <v>-0.06315954518423661</v>
       </c>
       <c r="D87">
-        <v>0.01492946176784351</v>
+        <v>0.01492946176784532</v>
       </c>
       <c r="E87">
         <v>1.5</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C88">
-        <v>-0.03117104195801372</v>
+        <v>-0.03117104195802143</v>
       </c>
       <c r="D88">
-        <v>0.007368116376053611</v>
+        <v>0.007368116376055377</v>
       </c>
       <c r="E88">
         <v>0.7</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.09686943926480054</v>
+        <v>-0.09686943926480858</v>
       </c>
       <c r="D89">
-        <v>0.02289770430990074</v>
+        <v>0.02289770430990246</v>
       </c>
       <c r="E89">
         <v>2.3</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="C90">
-        <v>0.1689199836974874</v>
+        <v>0.16891998369749</v>
       </c>
       <c r="D90">
-        <v>0.03992879351933847</v>
+        <v>0.03992879351933878</v>
       </c>
       <c r="E90">
         <v>4</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.1618728715050592</v>
+        <v>0.1618728715050619</v>
       </c>
       <c r="D91">
-        <v>0.03826301850870979</v>
+        <v>0.03826301850871014</v>
       </c>
       <c r="E91">
         <v>3.8</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.1581487403548675</v>
+        <v>0.1581487403548708</v>
       </c>
       <c r="D92">
-        <v>0.03738271968035303</v>
+        <v>0.03738271968035354</v>
       </c>
       <c r="E92">
         <v>3.7</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.1735035403230626</v>
+        <v>0.1735035403230645</v>
       </c>
       <c r="D93">
-        <v>0.04101224073547451</v>
+        <v>0.04101224073547466</v>
       </c>
       <c r="E93">
         <v>4.1</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>0.08426315033506887</v>
+        <v>0.08426315033506888</v>
       </c>
       <c r="D94">
         <v>0.02090336120626411</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="C95">
-        <v>0.09006680452590321</v>
+        <v>0.09006680452590329</v>
       </c>
       <c r="D95">
-        <v>0.02234308757995001</v>
+        <v>0.02234308757995003</v>
       </c>
       <c r="E95">
         <v>2.2</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.141840013484385</v>
+        <v>0.1418400134843849</v>
       </c>
       <c r="D96">
-        <v>0.03518659133411867</v>
+        <v>0.03518659133411861</v>
       </c>
       <c r="E96">
         <v>3.5</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.07085544066882365</v>
+        <v>-0.07085544066882338</v>
       </c>
       <c r="D97">
-        <v>0.01757727860683867</v>
+        <v>0.0175772786068386</v>
       </c>
       <c r="E97">
         <v>1.8</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C98">
-        <v>-0.1343264349016959</v>
+        <v>-0.1343264349016961</v>
       </c>
       <c r="D98">
-        <v>0.03332267992751848</v>
+        <v>0.03332267992751854</v>
       </c>
       <c r="E98">
         <v>3.3</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="C99">
-        <v>-0.2105766624757294</v>
+        <v>-0.2105766624757298</v>
       </c>
       <c r="D99">
-        <v>0.0522382562227536</v>
+        <v>0.0522382562227537</v>
       </c>
       <c r="E99">
         <v>5.2</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.155556852659324</v>
+        <v>0.1555568526593242</v>
       </c>
       <c r="D100">
-        <v>0.03858936043000245</v>
+        <v>0.0385893604300025</v>
       </c>
       <c r="E100">
         <v>3.9</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.2112267441940677</v>
+        <v>0.2112267441940679</v>
       </c>
       <c r="D101">
-        <v>0.05239952354919439</v>
+        <v>0.05239952354919442</v>
       </c>
       <c r="E101">
         <v>5.2</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.390834112466945</v>
+        <v>0.3908341124669448</v>
       </c>
       <c r="D102">
-        <v>0.09695515290063984</v>
+        <v>0.09695515290063977</v>
       </c>
       <c r="E102">
         <v>9.699999999999999</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.08484047021598283</v>
+        <v>0.08484047021598258</v>
       </c>
       <c r="D103">
-        <v>0.02104657832969605</v>
+        <v>0.02104657832969599</v>
       </c>
       <c r="E103">
         <v>2.1</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.07790268864985951</v>
+        <v>0.07790268864985944</v>
       </c>
       <c r="D104">
-        <v>0.01932550626592727</v>
+        <v>0.01932550626592725</v>
       </c>
       <c r="E104">
         <v>1.9</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.08944089918214938</v>
+        <v>0.08944089918214933</v>
       </c>
       <c r="D105">
-        <v>0.02218781774456656</v>
+        <v>0.02218781774456655</v>
       </c>
       <c r="E105">
         <v>2.2</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.1371855342600627</v>
+        <v>0.1371855342600629</v>
       </c>
       <c r="D107">
-        <v>0.0340319435424544</v>
+        <v>0.03403194354245443</v>
       </c>
       <c r="E107">
         <v>3.4</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.1841922083160854</v>
+        <v>0.1841922083160856</v>
       </c>
       <c r="D108">
-        <v>0.04569300158491909</v>
+        <v>0.04569300158491913</v>
       </c>
       <c r="E108">
         <v>4.6</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.1938221091838426</v>
+        <v>0.1938221091838427</v>
       </c>
       <c r="D109">
-        <v>0.04808191412164237</v>
+        <v>0.0480819141216424</v>
       </c>
       <c r="E109">
         <v>4.8</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="C110">
-        <v>-0.04478336458789415</v>
+        <v>-0.04478336458789399</v>
       </c>
       <c r="D110">
-        <v>0.01110951634599603</v>
+        <v>0.01110951634599599</v>
       </c>
       <c r="E110">
         <v>1.1</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="C111">
-        <v>-0.04978538056816222</v>
+        <v>-0.04978538056816195</v>
       </c>
       <c r="D111">
-        <v>0.01235037841178961</v>
+        <v>0.01235037841178954</v>
       </c>
       <c r="E111">
         <v>1.2</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>-0.0432719831219907</v>
+        <v>-0.04327198312199045</v>
       </c>
       <c r="D112">
-        <v>0.01073458433150803</v>
+        <v>0.01073458433150796</v>
       </c>
       <c r="E112">
         <v>1.1</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.3615074865137196</v>
+        <v>-0.3615074865137199</v>
       </c>
       <c r="D113">
-        <v>0.08968002667021049</v>
+        <v>0.08968002667021056</v>
       </c>
       <c r="E113">
         <v>9</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.3629325507255409</v>
+        <v>-0.3629325507255411</v>
       </c>
       <c r="D114">
-        <v>0.09003354575706361</v>
+        <v>0.09003354575706367</v>
       </c>
       <c r="E114">
         <v>9</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="C115">
-        <v>-0.3691544431616144</v>
+        <v>-0.3691544431616147</v>
       </c>
       <c r="D115">
-        <v>0.09157702549239982</v>
+        <v>0.09157702549239989</v>
       </c>
       <c r="E115">
         <v>9.199999999999999</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="C116">
-        <v>-0.3481915950117452</v>
+        <v>-0.3481915950117454</v>
       </c>
       <c r="D116">
-        <v>0.08637672162236504</v>
+        <v>0.08637672162236508</v>
       </c>
       <c r="E116">
         <v>8.6</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="C117">
-        <v>-0.06626151181255109</v>
+        <v>-0.06626151181255148</v>
       </c>
       <c r="D117">
-        <v>0.01885863625377085</v>
+        <v>0.01885863625377096</v>
       </c>
       <c r="E117">
         <v>1.9</v>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="C118">
-        <v>-0.02347797916435805</v>
+        <v>-0.02347797916435819</v>
       </c>
       <c r="D118">
-        <v>0.006682049004356891</v>
+        <v>0.006682049004356932</v>
       </c>
       <c r="E118">
         <v>0.7</v>
@@ -2856,7 +2856,7 @@
         <v>0.1717108870334541</v>
       </c>
       <c r="D119">
-        <v>0.0488704991901931</v>
+        <v>0.04887049919019312</v>
       </c>
       <c r="E119">
         <v>4.9</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.09970565563722207</v>
+        <v>-0.09970565563722258</v>
       </c>
       <c r="D120">
-        <v>0.02837714746722612</v>
+        <v>0.02837714746722627</v>
       </c>
       <c r="E120">
         <v>2.8</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="C121">
-        <v>0.04716481226549594</v>
+        <v>0.04716481226549566</v>
       </c>
       <c r="D121">
-        <v>0.01342353976179423</v>
+        <v>0.01342353976179415</v>
       </c>
       <c r="E121">
         <v>1.3</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C122">
-        <v>0.1956460066297784</v>
+        <v>0.1956460066297788</v>
       </c>
       <c r="D122">
-        <v>0.05568265456984264</v>
+        <v>0.05568265456984276</v>
       </c>
       <c r="E122">
         <v>5.6</v>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="C123">
-        <v>-0.02993339518845596</v>
+        <v>-0.02993339518845623</v>
       </c>
       <c r="D123">
-        <v>0.008519319832248963</v>
+        <v>0.008519319832249041</v>
       </c>
       <c r="E123">
         <v>0.9</v>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="C124">
-        <v>-0.06326970308536035</v>
+        <v>-0.06326970308536012</v>
       </c>
       <c r="D124">
-        <v>0.01800713994794313</v>
+        <v>0.01800713994794306</v>
       </c>
       <c r="E124">
         <v>1.8</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="C125">
-        <v>0.06604840498359313</v>
+        <v>0.0660484049835933</v>
       </c>
       <c r="D125">
-        <v>0.01879798408842512</v>
+        <v>0.01879798408842517</v>
       </c>
       <c r="E125">
         <v>1.9</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="C126">
-        <v>0.3688381832420802</v>
+        <v>0.36883818324208</v>
       </c>
       <c r="D126">
-        <v>0.1049747424106693</v>
+        <v>0.1049747424106692</v>
       </c>
       <c r="E126">
         <v>10.5</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="C127">
-        <v>0.3916254182748141</v>
+        <v>0.3916254182748135</v>
       </c>
       <c r="D127">
-        <v>0.1114601992762959</v>
+        <v>0.1114601992762958</v>
       </c>
       <c r="E127">
         <v>11.1</v>
@@ -3045,7 +3045,7 @@
         <v>0.338252060539984</v>
       </c>
       <c r="D128">
-        <v>0.09626965031914266</v>
+        <v>0.09626965031914267</v>
       </c>
       <c r="E128">
         <v>9.6</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="C129">
-        <v>-0.04507926609120332</v>
+        <v>-0.04507926609120322</v>
       </c>
       <c r="D129">
-        <v>0.01282997412141628</v>
+        <v>0.01282997412141626</v>
       </c>
       <c r="E129">
         <v>1.3</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="C130">
-        <v>-0.06466960284839739</v>
+        <v>-0.06466960284839701</v>
       </c>
       <c r="D130">
-        <v>0.01840556430773648</v>
+        <v>0.01840556430773638</v>
       </c>
       <c r="E130">
         <v>1.8</v>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="C131">
-        <v>-0.01710950675427131</v>
+        <v>-0.01710950675427117</v>
       </c>
       <c r="D131">
-        <v>0.004869523129400138</v>
+        <v>0.004869523129400102</v>
       </c>
       <c r="E131">
         <v>0.5</v>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="C132">
-        <v>-0.07113761907116974</v>
+        <v>-0.07113761907116968</v>
       </c>
       <c r="D132">
-        <v>0.02024642126816653</v>
+        <v>0.02024642126816652</v>
       </c>
       <c r="E132">
         <v>2</v>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="C133">
-        <v>-0.3997212379396929</v>
+        <v>-0.3997212379396923</v>
       </c>
       <c r="D133">
-        <v>0.113764344081624</v>
+        <v>0.1137643440816238</v>
       </c>
       <c r="E133">
         <v>11.4</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="C134">
-        <v>-0.3952537413080145</v>
+        <v>-0.3952537413080143</v>
       </c>
       <c r="D134">
-        <v>0.1124928534132537</v>
+        <v>0.1124928534132536</v>
       </c>
       <c r="E134">
         <v>11.2</v>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="C135">
-        <v>-0.3906505862441595</v>
+        <v>-0.3906505862441594</v>
       </c>
       <c r="D135">
         <v>0.111182753106238</v>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="C136">
-        <v>0.08362111401778236</v>
+        <v>0.08362111401778234</v>
       </c>
       <c r="D136">
-        <v>0.02379933885084928</v>
+        <v>0.02379933885084929</v>
       </c>
       <c r="E136">
         <v>2.4</v>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="C137">
-        <v>0.02274398081913845</v>
+        <v>0.02274398081913823</v>
       </c>
       <c r="D137">
-        <v>0.006473146318246667</v>
+        <v>0.006473146318246607</v>
       </c>
       <c r="E137">
         <v>0.6</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="C139">
-        <v>0.106193892211046</v>
+        <v>0.1061938922110461</v>
       </c>
       <c r="D139">
-        <v>0.03022375932571047</v>
+        <v>0.0302237593257105</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="C140">
-        <v>-0.2669941352345404</v>
+        <v>-0.2669941352345399</v>
       </c>
       <c r="D140">
-        <v>0.08530457502425554</v>
+        <v>0.0853045750242554</v>
       </c>
       <c r="E140">
         <v>8.5</v>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="C141">
-        <v>-0.110077809117979</v>
+        <v>-0.1100778091179791</v>
       </c>
       <c r="D141">
-        <v>0.03516983891111156</v>
+        <v>0.03516983891111159</v>
       </c>
       <c r="E141">
         <v>3.5</v>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="C142">
-        <v>0.3744778659758282</v>
+        <v>0.3744778659758274</v>
       </c>
       <c r="D142">
-        <v>0.119645606391303</v>
+        <v>0.1196456063913028</v>
       </c>
       <c r="E142">
         <v>12</v>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="C143">
-        <v>-0.5172266792656476</v>
+        <v>-0.5172266792656469</v>
       </c>
       <c r="D143">
-        <v>0.1652538248722366</v>
+        <v>0.1652538248722364</v>
       </c>
       <c r="E143">
         <v>16.5</v>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="C144">
-        <v>-0.1850794474876874</v>
+        <v>-0.1850794474876873</v>
       </c>
       <c r="D144">
-        <v>0.0591328479923057</v>
+        <v>0.05913284799230569</v>
       </c>
       <c r="E144">
         <v>5.9</v>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="C145">
-        <v>0.5984937300875335</v>
+        <v>0.5984937300875331</v>
       </c>
       <c r="D145">
-        <v>0.1912186320308124</v>
+        <v>0.1912186320308123</v>
       </c>
       <c r="E145">
         <v>19.1</v>
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="C146">
-        <v>-0.05197147141039617</v>
+        <v>-0.05197147141039647</v>
       </c>
       <c r="D146">
-        <v>0.01660487515261179</v>
+        <v>0.01660487515261189</v>
       </c>
       <c r="E146">
         <v>1.7</v>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="C147">
-        <v>-0.02219227220854736</v>
+        <v>-0.02219227220854754</v>
       </c>
       <c r="D147">
-        <v>0.007090426716338685</v>
+        <v>0.007090426716338746</v>
       </c>
       <c r="E147">
         <v>0.7</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="C148">
-        <v>-0.0111954850695259</v>
+        <v>-0.01119548506952499</v>
       </c>
       <c r="D148">
-        <v>0.003576955333522079</v>
+        <v>0.00357695533352179</v>
       </c>
       <c r="E148">
         <v>0.4</v>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="C149">
-        <v>-0.05200490408662976</v>
+        <v>-0.05200490408662979</v>
       </c>
       <c r="D149">
-        <v>0.01661555688625933</v>
+        <v>0.01661555688625934</v>
       </c>
       <c r="E149">
         <v>1.7</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="C150">
-        <v>-0.1015471158565625</v>
+        <v>-0.1015471158565631</v>
       </c>
       <c r="D150">
-        <v>0.03244428404943579</v>
+        <v>0.03244428404943601</v>
       </c>
       <c r="E150">
         <v>3.2</v>
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="C151">
-        <v>-0.01061925700908253</v>
+        <v>-0.01061925700908239</v>
       </c>
       <c r="D151">
-        <v>0.003392850578674215</v>
+        <v>0.00339285057867417</v>
       </c>
       <c r="E151">
         <v>0.3</v>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="C152">
-        <v>0.06394932420346064</v>
+        <v>0.06394932420346006</v>
       </c>
       <c r="D152">
-        <v>0.02043179682382336</v>
+        <v>0.02043179682382318</v>
       </c>
       <c r="E152">
         <v>2</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="C153">
-        <v>0.02034516631611459</v>
+        <v>0.0203451663161151</v>
       </c>
       <c r="D153">
-        <v>0.006500276737799413</v>
+        <v>0.006500276737799578</v>
       </c>
       <c r="E153">
         <v>0.7</v>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="C154">
-        <v>0.03110757513971094</v>
+        <v>0.03110757513971121</v>
       </c>
       <c r="D154">
-        <v>0.009938864293768375</v>
+        <v>0.009938864293768463</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="C155">
-        <v>0.09381425707810724</v>
+        <v>0.0938142570781071</v>
       </c>
       <c r="D155">
-        <v>0.02997363715212008</v>
+        <v>0.02997363715212005</v>
       </c>
       <c r="E155">
         <v>3</v>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="C156">
-        <v>0.1481155738678649</v>
+        <v>0.1481155738678647</v>
       </c>
       <c r="D156">
-        <v>0.04732289745680299</v>
+        <v>0.04732289745680294</v>
       </c>
       <c r="E156">
         <v>4.7</v>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="C157">
-        <v>0.05524447412291626</v>
+        <v>0.05524447412291654</v>
       </c>
       <c r="D157">
-        <v>0.01765059889182238</v>
+        <v>0.01765059889182247</v>
       </c>
       <c r="E157">
         <v>1.8</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="C158">
-        <v>0.2207308224977233</v>
+        <v>0.2207308224977236</v>
       </c>
       <c r="D158">
-        <v>0.07052345547358958</v>
+        <v>0.07052345547358972</v>
       </c>
       <c r="E158">
         <v>7.1</v>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="C159">
-        <v>-0.02502505349855397</v>
+        <v>-0.02502505349855415</v>
       </c>
       <c r="D159">
-        <v>0.007995499795447334</v>
+        <v>0.007995499795447392</v>
       </c>
       <c r="E159">
         <v>0.8</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="C160">
-        <v>-0.06413672564241563</v>
+        <v>-0.06413672564241554</v>
       </c>
       <c r="D160">
-        <v>0.02049167154764434</v>
+        <v>0.02049167154764432</v>
       </c>
       <c r="E160">
         <v>2</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="C161">
-        <v>-0.08148415032382966</v>
+        <v>-0.08148415032382948</v>
       </c>
       <c r="D161">
-        <v>0.02603417040782854</v>
+        <v>0.02603417040782849</v>
       </c>
       <c r="E161">
         <v>2.6</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="C162">
-        <v>0.0240590362836962</v>
+        <v>0.0240590362836964</v>
       </c>
       <c r="D162">
-        <v>0.00768685748048724</v>
+        <v>0.007686857480487304</v>
       </c>
       <c r="E162">
         <v>0.8</v>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="C163">
-        <v>-0.1596650506659057</v>
+        <v>-0.1596650506659056</v>
       </c>
       <c r="D163">
         <v>0.04833343600420724</v>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="C164">
-        <v>-0.2632537843199246</v>
+        <v>-0.2632537843199241</v>
       </c>
       <c r="D164">
-        <v>0.07969157861551653</v>
+        <v>0.07969157861551641</v>
       </c>
       <c r="E164">
         <v>8</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="C165">
-        <v>0.345429072266942</v>
+        <v>0.3454290722669419</v>
       </c>
       <c r="D165">
         <v>0.1045674923145349</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="C166">
-        <v>0.2626123650098522</v>
+        <v>0.262612365009852</v>
       </c>
       <c r="D166">
-        <v>0.07949740964086648</v>
+        <v>0.07949740964086646</v>
       </c>
       <c r="E166">
         <v>7.9</v>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="C167">
-        <v>0.0316773352917717</v>
+        <v>0.03167733529177191</v>
       </c>
       <c r="D167">
-        <v>0.009589289902349328</v>
+        <v>0.009589289902349394</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="C168">
-        <v>-0.1162146085733191</v>
+        <v>-0.1162146085733198</v>
       </c>
       <c r="D168">
-        <v>0.03518021835590071</v>
+        <v>0.03518021835590095</v>
       </c>
       <c r="E168">
         <v>3.5</v>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="C169">
-        <v>-0.3710537399601885</v>
+        <v>-0.3710537399601881</v>
       </c>
       <c r="D169">
-        <v>0.1123245326368544</v>
+        <v>0.1123245326368543</v>
       </c>
       <c r="E169">
         <v>11.2</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="C170">
-        <v>-0.3735251185177073</v>
+        <v>-0.373525118517707</v>
       </c>
       <c r="D170">
         <v>0.1130726626556269</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="C171">
-        <v>0.5934724744638876</v>
+        <v>0.5934724744638872</v>
       </c>
       <c r="D171">
         <v>0.1796546191237581</v>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="C172">
-        <v>-0.04920041551103364</v>
+        <v>-0.04920041551103338</v>
       </c>
       <c r="D172">
-        <v>0.01489383634405313</v>
+        <v>0.01489383634405306</v>
       </c>
       <c r="E172">
         <v>1.5</v>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="C173">
-        <v>0.01629103798449721</v>
+        <v>0.01629103798449769</v>
       </c>
       <c r="D173">
-        <v>0.004931585457066744</v>
+        <v>0.004931585457066892</v>
       </c>
       <c r="E173">
         <v>0.5</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="C174">
-        <v>-0.09215585368860192</v>
+        <v>-0.09215585368860182</v>
       </c>
       <c r="D174">
-        <v>0.0278972075485162</v>
+        <v>0.02789720754851619</v>
       </c>
       <c r="E174">
         <v>2.8</v>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="C175">
-        <v>-0.0118730520884265</v>
+        <v>-0.01187305208842672</v>
       </c>
       <c r="D175">
-        <v>0.003594182952983102</v>
+        <v>0.003594182952983169</v>
       </c>
       <c r="E175">
         <v>0.4</v>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="C176">
-        <v>-0.0258422974001587</v>
+        <v>-0.02584229740015852</v>
       </c>
       <c r="D176">
-        <v>0.007822920685415714</v>
+        <v>0.007822920685415664</v>
       </c>
       <c r="E176">
         <v>0.8</v>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="C177">
-        <v>0.02854700495437036</v>
+        <v>0.02854700495437014</v>
       </c>
       <c r="D177">
-        <v>0.008641683520089719</v>
+        <v>0.008641683520089654</v>
       </c>
       <c r="E177">
         <v>0.9</v>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="C178">
-        <v>-0.03722527886857907</v>
+        <v>-0.03722527886857901</v>
       </c>
       <c r="D178">
-        <v>0.01126875059024695</v>
+        <v>0.01126875059024694</v>
       </c>
       <c r="E178">
         <v>1.1</v>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="C179">
-        <v>0.05111722383997355</v>
+        <v>0.05111722383997325</v>
       </c>
       <c r="D179">
-        <v>0.01547408814188086</v>
+        <v>0.01547408814188078</v>
       </c>
       <c r="E179">
         <v>1.5</v>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="C180">
-        <v>0.1806800306692091</v>
+        <v>0.1806800306692089</v>
       </c>
       <c r="D180">
-        <v>0.05469504229740121</v>
+        <v>0.05469504229740118</v>
       </c>
       <c r="E180">
         <v>5.5</v>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="C181">
-        <v>-0.04803856775231431</v>
+        <v>-0.04803856775231449</v>
       </c>
       <c r="D181">
-        <v>0.01454212446935991</v>
+        <v>0.01454212446935998</v>
       </c>
       <c r="E181">
         <v>1.5</v>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="C182">
-        <v>0.03312923164770894</v>
+        <v>0.03312923164770916</v>
       </c>
       <c r="D182">
-        <v>0.01002880461963879</v>
+        <v>0.01002880461963887</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="C183">
-        <v>0.1047234278783309</v>
+        <v>0.1047234278783303</v>
       </c>
       <c r="D183">
-        <v>0.03170163463067352</v>
+        <v>0.03170163463067337</v>
       </c>
       <c r="E183">
         <v>3.2</v>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="C184">
-        <v>0.09495586985207176</v>
+        <v>0.09495586985207188</v>
       </c>
       <c r="D184">
-        <v>0.02874482198563556</v>
+        <v>0.02874482198563562</v>
       </c>
       <c r="E184">
         <v>2.9</v>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="C185">
-        <v>-0.01272498297738019</v>
+        <v>-0.01272498297738028</v>
       </c>
       <c r="D185">
-        <v>0.003852077507423894</v>
+        <v>0.003852077507423924</v>
       </c>
       <c r="E185">
         <v>0.4</v>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="C186">
-        <v>-0.01934594281344285</v>
+        <v>-0.0193459428134443</v>
       </c>
       <c r="D186">
-        <v>0.005629980079319446</v>
+        <v>0.005629980079319877</v>
       </c>
       <c r="E186">
         <v>0.6</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="C187">
-        <v>-0.01354721308776045</v>
+        <v>-0.01354721308775858</v>
       </c>
       <c r="D187">
-        <v>0.003942456594123145</v>
+        <v>0.003942456594122607</v>
       </c>
       <c r="E187">
         <v>0.4</v>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="C188">
-        <v>0.01007561055988125</v>
+        <v>0.01007561055988077</v>
       </c>
       <c r="D188">
-        <v>0.002932164500129477</v>
+        <v>0.002932164500129343</v>
       </c>
       <c r="E188">
         <v>0.3</v>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="C189">
-        <v>0.02986650438909792</v>
+        <v>0.02986650438909581</v>
       </c>
       <c r="D189">
-        <v>0.008691632471522029</v>
+        <v>0.008691632471521427</v>
       </c>
       <c r="E189">
         <v>0.9</v>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="C190">
-        <v>0.07160171137217836</v>
+        <v>0.07160171137218191</v>
       </c>
       <c r="D190">
-        <v>0.02083724802445052</v>
+        <v>0.02083724802445159</v>
       </c>
       <c r="E190">
         <v>2.1</v>
@@ -4365,10 +4365,10 @@
         </is>
       </c>
       <c r="C191">
-        <v>-0.1429442020540198</v>
+        <v>-0.1429442020540212</v>
       </c>
       <c r="D191">
-        <v>0.04159905866459687</v>
+        <v>0.04159905866459735</v>
       </c>
       <c r="E191">
         <v>4.2</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="C192">
-        <v>-0.04379797735035138</v>
+        <v>-0.04379797735035206</v>
       </c>
       <c r="D192">
-        <v>0.01274591486053712</v>
+        <v>0.01274591486053734</v>
       </c>
       <c r="E192">
         <v>1.3</v>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="C193">
-        <v>-0.06649692306068833</v>
+        <v>-0.06649692306068793</v>
       </c>
       <c r="D193">
-        <v>0.01935167263637167</v>
+        <v>0.01935167263637158</v>
       </c>
       <c r="E193">
         <v>1.9</v>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="C194">
-        <v>0.1433994288646637</v>
+        <v>0.1433994288646641</v>
       </c>
       <c r="D194">
-        <v>0.0417315369780196</v>
+        <v>0.04173153697801976</v>
       </c>
       <c r="E194">
         <v>4.2</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="C195">
-        <v>0.02859053267677523</v>
+        <v>0.02859053267677467</v>
       </c>
       <c r="D195">
-        <v>0.008320304209496974</v>
+        <v>0.00832030420949682</v>
       </c>
       <c r="E195">
         <v>0.8</v>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="C196">
-        <v>-0.5053437322452923</v>
+        <v>-0.5053437322452921</v>
       </c>
       <c r="D196">
-        <v>0.1470631425506431</v>
+        <v>0.1470631425506433</v>
       </c>
       <c r="E196">
         <v>14.7</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="C197">
-        <v>0.4646975701635828</v>
+        <v>0.4646975701635825</v>
       </c>
       <c r="D197">
-        <v>0.1352344565554689</v>
+        <v>0.135234456555469</v>
       </c>
       <c r="E197">
         <v>13.5</v>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="C198">
-        <v>-0.08716392671709436</v>
+        <v>-0.08716392671709353</v>
       </c>
       <c r="D198">
-        <v>0.02536610263892172</v>
+        <v>0.02536610263892151</v>
       </c>
       <c r="E198">
         <v>2.5</v>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C199">
-        <v>0.221134890041677</v>
+        <v>0.2211348900416761</v>
       </c>
       <c r="D199">
-        <v>0.06435380471155117</v>
+        <v>0.064353804711551</v>
       </c>
       <c r="E199">
         <v>6.4</v>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="C200">
-        <v>-0.3051912497382263</v>
+        <v>-0.3051912497382254</v>
       </c>
       <c r="D200">
-        <v>0.08881555543598972</v>
+        <v>0.0888155554359896</v>
       </c>
       <c r="E200">
         <v>8.9</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="C201">
-        <v>0.1428024821387861</v>
+        <v>0.1428024821387859</v>
       </c>
       <c r="D201">
-        <v>0.0415578158930606</v>
+        <v>0.04155781589306059</v>
       </c>
       <c r="E201">
         <v>4.2</v>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="C202">
-        <v>-0.007130957205334501</v>
+        <v>-0.007130957205334577</v>
       </c>
       <c r="D202">
-        <v>0.002075223079053857</v>
+        <v>0.002075223079053883</v>
       </c>
       <c r="E202">
         <v>0.2</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="C203">
-        <v>-0.3899905822625923</v>
+        <v>-0.3899905822625911</v>
       </c>
       <c r="D203">
-        <v>0.1134935231864177</v>
+        <v>0.1134935231864175</v>
       </c>
       <c r="E203">
         <v>11.3</v>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="C204">
-        <v>0.3003661967379388</v>
+        <v>0.3003661967379375</v>
       </c>
       <c r="D204">
-        <v>0.08741138751637802</v>
+        <v>0.08741138751637775</v>
       </c>
       <c r="E204">
         <v>8.699999999999999</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="C205">
-        <v>0.03372690600708388</v>
+        <v>0.03372690600708405</v>
       </c>
       <c r="D205">
-        <v>0.009815071345347879</v>
+        <v>0.009815071345347941</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="C206">
-        <v>0.08333087826419007</v>
+        <v>0.08333087826419003</v>
       </c>
       <c r="D206">
-        <v>0.02425062397546148</v>
+        <v>0.02425062397546151</v>
       </c>
       <c r="E206">
         <v>2.4</v>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="C207">
-        <v>-0.1498622134497501</v>
+        <v>-0.1498622134497489</v>
       </c>
       <c r="D207">
-        <v>0.04361231109287359</v>
+        <v>0.04361231109287331</v>
       </c>
       <c r="E207">
         <v>4.4</v>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="C208">
-        <v>0.1758288280556604</v>
+        <v>0.1758288280556596</v>
       </c>
       <c r="D208">
-        <v>0.05116901300026562</v>
+        <v>0.05116901300026545</v>
       </c>
       <c r="E208">
         <v>5.1</v>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="C209">
-        <v>-0.3320165784960784</v>
+        <v>-0.3320165784960781</v>
       </c>
       <c r="D209">
-        <v>0.1122756040274674</v>
+        <v>0.1122756040274672</v>
       </c>
       <c r="E209">
         <v>11.2</v>
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="C210">
-        <v>0.3680057090887081</v>
+        <v>0.3680057090887079</v>
       </c>
       <c r="D210">
-        <v>0.1244457835830001</v>
+        <v>0.124445783583</v>
       </c>
       <c r="E210">
         <v>12.4</v>
@@ -4785,10 +4785,10 @@
         </is>
       </c>
       <c r="C211">
-        <v>-0.07249426683203758</v>
+        <v>-0.07249426683203769</v>
       </c>
       <c r="D211">
-        <v>0.02451485294488556</v>
+        <v>0.02451485294488558</v>
       </c>
       <c r="E211">
         <v>2.5</v>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="C212">
-        <v>-0.4520185710871827</v>
+        <v>-0.4520185710871835</v>
       </c>
       <c r="D212">
-        <v>0.1528557951242353</v>
+        <v>0.1528557951242355</v>
       </c>
       <c r="E212">
         <v>15.3</v>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="C213">
-        <v>0.6397890024664912</v>
+        <v>0.6397890024664903</v>
       </c>
       <c r="D213">
-        <v>0.2163527406596191</v>
+        <v>0.2163527406596187</v>
       </c>
       <c r="E213">
         <v>21.6</v>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="C214">
-        <v>-0.2385414158040015</v>
+        <v>-0.2385414158040002</v>
       </c>
       <c r="D214">
-        <v>0.08066579586560571</v>
+        <v>0.08066579586560525</v>
       </c>
       <c r="E214">
         <v>8.1</v>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C215">
-        <v>-0.1782689515755227</v>
+        <v>-0.1782689515755219</v>
       </c>
       <c r="D215">
-        <v>0.06028390000326913</v>
+        <v>0.06028390000326881</v>
       </c>
       <c r="E215">
         <v>6</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="C216">
-        <v>0.05997518105996215</v>
+        <v>0.05997518105996275</v>
       </c>
       <c r="D216">
-        <v>0.02028136580006202</v>
+        <v>0.02028136580006221</v>
       </c>
       <c r="E216">
         <v>2</v>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="C217">
-        <v>0.1130102837993388</v>
+        <v>0.1130102837993375</v>
       </c>
       <c r="D217">
-        <v>0.03821585636584753</v>
+        <v>0.03821585636584707</v>
       </c>
       <c r="E217">
         <v>3.8</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="C218">
-        <v>-0.005452179411610437</v>
+        <v>-0.005452179411610851</v>
       </c>
       <c r="D218">
-        <v>0.001843723405251325</v>
+        <v>0.001843723405251464</v>
       </c>
       <c r="E218">
         <v>0.2</v>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="C219">
-        <v>-0.02335610667703295</v>
+        <v>-0.02335610667703047</v>
       </c>
       <c r="D219">
-        <v>0.007898162786846536</v>
+        <v>0.007898162786845696</v>
       </c>
       <c r="E219">
         <v>0.8</v>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="C220">
-        <v>-0.005288088711718568</v>
+        <v>-0.005288088711720887</v>
       </c>
       <c r="D220">
-        <v>0.00178823406032433</v>
+        <v>0.001788234060325114</v>
       </c>
       <c r="E220">
         <v>0.2</v>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="C221">
-        <v>0.02876615651181526</v>
+        <v>0.02876615651181466</v>
       </c>
       <c r="D221">
-        <v>0.009727639543008152</v>
+        <v>0.009727639543007946</v>
       </c>
       <c r="E221">
         <v>1</v>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="C222">
-        <v>-0.02339920916783216</v>
+        <v>-0.02339920916783214</v>
       </c>
       <c r="D222">
-        <v>0.007912738439097065</v>
+        <v>0.007912738439097056</v>
       </c>
       <c r="E222">
         <v>0.8</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C223">
-        <v>0.05914608562127585</v>
+        <v>0.05914608562127827</v>
       </c>
       <c r="D223">
-        <v>0.020000996694409</v>
+        <v>0.0200009966944098</v>
       </c>
       <c r="E223">
         <v>2</v>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="C224">
-        <v>0.003686322668964705</v>
+        <v>0.003686322668963321</v>
       </c>
       <c r="D224">
-        <v>0.001246576620278757</v>
+        <v>0.001246576620278288</v>
       </c>
       <c r="E224">
         <v>0.1</v>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="C225">
-        <v>0.02394596770723119</v>
+        <v>0.02394596770723088</v>
       </c>
       <c r="D225">
-        <v>0.008097631752395657</v>
+        <v>0.008097631752395551</v>
       </c>
       <c r="E225">
         <v>0.8</v>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="C226">
-        <v>0.1029097101780823</v>
+        <v>0.1029097101780838</v>
       </c>
       <c r="D226">
-        <v>0.03480021968442842</v>
+        <v>0.03480021968442892</v>
       </c>
       <c r="E226">
         <v>3.5</v>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="C227">
-        <v>-0.04888953409355735</v>
+        <v>-0.04888953409355831</v>
       </c>
       <c r="D227">
-        <v>0.01653261411173914</v>
+        <v>0.01653261411173946</v>
       </c>
       <c r="E227">
         <v>1.7</v>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="C228">
-        <v>0.04055264341007321</v>
+        <v>0.04055264341007297</v>
       </c>
       <c r="D228">
-        <v>0.01371338911568912</v>
+        <v>0.01371338911568904</v>
       </c>
       <c r="E228">
         <v>1.4</v>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="C229">
-        <v>-0.04838337211624172</v>
+        <v>-0.04838337211624218</v>
       </c>
       <c r="D229">
-        <v>0.01636144903921093</v>
+        <v>0.01636144903921108</v>
       </c>
       <c r="E229">
         <v>1.6</v>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="C230">
-        <v>0.0856618401859351</v>
+        <v>0.08566184018593587</v>
       </c>
       <c r="D230">
-        <v>0.02896763436496242</v>
+        <v>0.02896763436496266</v>
       </c>
       <c r="E230">
         <v>2.9</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="C231">
-        <v>-0.003599735305063779</v>
+        <v>-0.003599735305064689</v>
       </c>
       <c r="D231">
-        <v>0.001217296008367272</v>
+        <v>0.001217296008367579</v>
       </c>
       <c r="E231">
         <v>0.1</v>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="C232">
-        <v>-0.122581312010419</v>
+        <v>-0.1225813120104498</v>
       </c>
       <c r="D232">
-        <v>0.03591191640754658</v>
+        <v>0.03591191640755433</v>
       </c>
       <c r="E232">
         <v>3.6</v>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="C233">
-        <v>0.1126984517879606</v>
+        <v>0.1126984517879877</v>
       </c>
       <c r="D233">
-        <v>0.03301659374901421</v>
+        <v>0.03301659374902098</v>
       </c>
       <c r="E233">
         <v>3.3</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="C234">
-        <v>-0.0004416488685710108</v>
+        <v>-0.0004416488685710443</v>
       </c>
       <c r="D234">
-        <v>0.000129387236842934</v>
+        <v>0.0001293872368429392</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="C235">
-        <v>0.1555505950782987</v>
+        <v>0.1555505950783284</v>
       </c>
       <c r="D235">
-        <v>0.04557073077437113</v>
+        <v>0.04557073077437823</v>
       </c>
       <c r="E235">
         <v>4.6</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="C236">
-        <v>-0.1901933520321061</v>
+        <v>-0.190193352032135</v>
       </c>
       <c r="D236">
-        <v>0.05571981281182183</v>
+        <v>0.05571981281182833</v>
       </c>
       <c r="E236">
         <v>5.6</v>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="C237">
-        <v>0.02867056120434252</v>
+        <v>0.02867056120434845</v>
       </c>
       <c r="D237">
-        <v>0.008399443442408928</v>
+        <v>0.00839944344241037</v>
       </c>
       <c r="E237">
         <v>0.8</v>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="C238">
-        <v>-0.2574883128050438</v>
+        <v>-0.2574883128051029</v>
       </c>
       <c r="D238">
-        <v>0.07543481639835105</v>
+        <v>0.07543481639836568</v>
       </c>
       <c r="E238">
         <v>7.5</v>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C239">
-        <v>0.2792438517409293</v>
+        <v>0.2792438517409854</v>
       </c>
       <c r="D239">
-        <v>0.08180840697959918</v>
+        <v>0.08180840697961272</v>
       </c>
       <c r="E239">
         <v>8.199999999999999</v>
@@ -5394,10 +5394,10 @@
         </is>
       </c>
       <c r="C240">
-        <v>-0.0265287155047389</v>
+        <v>-0.02652871550474362</v>
       </c>
       <c r="D240">
-        <v>0.007771959672978474</v>
+        <v>0.007771959672979584</v>
       </c>
       <c r="E240">
         <v>0.8</v>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="C241">
-        <v>0.03373503119070557</v>
+        <v>0.03373503119070721</v>
       </c>
       <c r="D241">
-        <v>0.009883151030587947</v>
+        <v>0.009883151030588079</v>
       </c>
       <c r="E241">
         <v>1</v>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="C242">
-        <v>-0.3427441127077892</v>
+        <v>-0.3427441127077734</v>
       </c>
       <c r="D242">
-        <v>0.1004116999799664</v>
+        <v>0.1004116999799583</v>
       </c>
       <c r="E242">
         <v>10</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="C243">
-        <v>0.3242088949586597</v>
+        <v>0.3242088949586462</v>
       </c>
       <c r="D243">
-        <v>0.09498154770401566</v>
+        <v>0.09498154770400834</v>
       </c>
       <c r="E243">
         <v>9.5</v>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="C244">
-        <v>0.07194211893172936</v>
+        <v>0.07194211893172253</v>
       </c>
       <c r="D244">
-        <v>0.02107645381572065</v>
+        <v>0.02107645381571791</v>
       </c>
       <c r="E244">
         <v>2.1</v>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="C245">
-        <v>-0.226627129420046</v>
+        <v>-0.2266271294200229</v>
       </c>
       <c r="D245">
-        <v>0.06639359943156081</v>
+        <v>0.06639359943155171</v>
       </c>
       <c r="E245">
         <v>6.6</v>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="C246">
-        <v>0.537863771204303</v>
+        <v>0.5378637712042624</v>
       </c>
       <c r="D246">
-        <v>0.1575747434363806</v>
+        <v>0.1575747434363631</v>
       </c>
       <c r="E246">
         <v>15.8</v>
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="C247">
-        <v>-0.4178861321347695</v>
+        <v>-0.417886132134742</v>
       </c>
       <c r="D247">
-        <v>0.1224256095726994</v>
+        <v>0.1224256095726871</v>
       </c>
       <c r="E247">
         <v>12.2</v>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="C248">
-        <v>0.00231934359840459</v>
+        <v>0.002319343598403575</v>
       </c>
       <c r="D248">
-        <v>0.0006794842709727595</v>
+        <v>0.0006794842709724381</v>
       </c>
       <c r="E248">
         <v>0.1</v>
@@ -5583,10 +5583,10 @@
         </is>
       </c>
       <c r="C249">
-        <v>-0.01388606584809857</v>
+        <v>-0.0138860658480933</v>
       </c>
       <c r="D249">
-        <v>0.004068117951978012</v>
+        <v>0.004068117951976324</v>
       </c>
       <c r="E249">
         <v>0.4</v>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="C250">
-        <v>0.008732688592362092</v>
+        <v>0.008732688592352789</v>
       </c>
       <c r="D250">
-        <v>0.002558363730968939</v>
+        <v>0.002558363730966123</v>
       </c>
       <c r="E250">
         <v>0.3</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="C251">
-        <v>0.0371759743643038</v>
+        <v>0.03717597436431302</v>
       </c>
       <c r="D251">
-        <v>0.01089122364448585</v>
+        <v>0.01089122364448817</v>
       </c>
       <c r="E251">
         <v>1.1</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="C252">
-        <v>-0.0587087471709983</v>
+        <v>-0.05870874717101893</v>
       </c>
       <c r="D252">
-        <v>0.01719955176052836</v>
+        <v>0.01719955176053379</v>
       </c>
       <c r="E252">
         <v>1.7</v>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="C253">
-        <v>0.122931477296748</v>
+        <v>0.1229314772967503</v>
       </c>
       <c r="D253">
-        <v>0.03601450224453292</v>
+        <v>0.03601450224453232</v>
       </c>
       <c r="E253">
         <v>3.6</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="C254">
-        <v>-0.04122992005596311</v>
+        <v>-0.04122992005594987</v>
       </c>
       <c r="D254">
-        <v>0.01207888395266748</v>
+        <v>0.01207888395266318</v>
       </c>
       <c r="E254">
         <v>1.2</v>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="C255">
-        <v>0.2588366742688571</v>
+        <v>0.2588366742688428</v>
       </c>
       <c r="D255">
-        <v>0.0715791662153354</v>
+        <v>0.07157916621533007</v>
       </c>
       <c r="E255">
         <v>7.2</v>
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="C256">
-        <v>-0.2284823944793775</v>
+        <v>-0.2284823944793639</v>
       </c>
       <c r="D256">
-        <v>0.06318493829328635</v>
+        <v>0.06318493829328138</v>
       </c>
       <c r="E256">
         <v>6.3</v>
@@ -5751,10 +5751,10 @@
         </is>
       </c>
       <c r="C257">
-        <v>-0.0004935743385530606</v>
+        <v>-0.0004935743385525854</v>
       </c>
       <c r="D257">
-        <v>0.0001364939482347713</v>
+        <v>0.0001364939482346373</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="C258">
-        <v>-0.2434067589913793</v>
+        <v>-0.2434067589913604</v>
       </c>
       <c r="D258">
-        <v>0.06731214928871582</v>
+        <v>0.06731214928870932</v>
       </c>
       <c r="E258">
         <v>6.7</v>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="C259">
-        <v>0.238714740555133</v>
+        <v>0.2387147405551102</v>
       </c>
       <c r="D259">
-        <v>0.06601460994858106</v>
+        <v>0.0660146099485735</v>
       </c>
       <c r="E259">
         <v>6.6</v>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="C260">
-        <v>-0.04748116793583265</v>
+        <v>-0.04748116793582947</v>
       </c>
       <c r="D260">
-        <v>0.01313052882238389</v>
+        <v>0.01313052882238276</v>
       </c>
       <c r="E260">
         <v>1.3</v>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="C261">
-        <v>0.4931444043647614</v>
+        <v>0.4931444043647305</v>
       </c>
       <c r="D261">
-        <v>0.1363750534498153</v>
+        <v>0.1363750534498042</v>
       </c>
       <c r="E261">
         <v>13.6</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="C262">
-        <v>-0.4668967385647553</v>
+        <v>-0.4668967385647219</v>
       </c>
       <c r="D262">
-        <v>0.1291164760539719</v>
+        <v>0.1291164760539602</v>
       </c>
       <c r="E262">
         <v>12.9</v>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="C263">
-        <v>0.04220172769055655</v>
+        <v>0.0422017276905528</v>
       </c>
       <c r="D263">
-        <v>0.01167054278328024</v>
+        <v>0.01167054278327899</v>
       </c>
       <c r="E263">
         <v>1.2</v>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="C264">
-        <v>-0.01578981080132696</v>
+        <v>-0.01578981080132296</v>
       </c>
       <c r="D264">
-        <v>0.00436654309150528</v>
+        <v>0.004366543091504091</v>
       </c>
       <c r="E264">
         <v>0.4</v>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="C265">
-        <v>-0.1339303136715794</v>
+        <v>-0.1339303136716201</v>
       </c>
       <c r="D265">
-        <v>0.03703733333249459</v>
+        <v>0.03703733333250514</v>
       </c>
       <c r="E265">
         <v>3.7</v>
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="C266">
-        <v>0.1126296060059171</v>
+        <v>0.112629606005956</v>
       </c>
       <c r="D266">
-        <v>0.03114679676609985</v>
+        <v>0.03114679676611001</v>
       </c>
       <c r="E266">
         <v>3.1</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="C267">
-        <v>0.05242401918656526</v>
+        <v>0.05242401918657416</v>
       </c>
       <c r="D267">
-        <v>0.01449743392674466</v>
+        <v>0.01449743392674685</v>
       </c>
       <c r="E267">
         <v>1.4</v>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="C268">
-        <v>-0.1882221330403255</v>
+        <v>-0.1882221330403543</v>
       </c>
       <c r="D268">
-        <v>0.05205129212989375</v>
+        <v>0.05205129212990071</v>
       </c>
       <c r="E268">
         <v>5.2</v>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="C269">
-        <v>0.3414149960894986</v>
+        <v>0.3414149960895634</v>
       </c>
       <c r="D269">
-        <v>0.09441552601666492</v>
+        <v>0.09441552601668107</v>
       </c>
       <c r="E269">
         <v>9.4</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="C270">
-        <v>-0.2353223521253231</v>
+        <v>-0.2353223521253725</v>
       </c>
       <c r="D270">
-        <v>0.0650764726619301</v>
+        <v>0.06507647266194254</v>
       </c>
       <c r="E270">
         <v>6.5</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="C271">
-        <v>0.01043723763974148</v>
+        <v>0.01043723763974154</v>
       </c>
       <c r="D271">
-        <v>0.002886332742275924</v>
+        <v>0.002886332742275885</v>
       </c>
       <c r="E271">
         <v>0.3</v>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="C272">
-        <v>-0.04262256719530495</v>
+        <v>-0.04262256719530679</v>
       </c>
       <c r="D272">
-        <v>0.01178692250785156</v>
+        <v>0.01178692250785185</v>
       </c>
       <c r="E272">
         <v>1.2</v>
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="C273">
-        <v>0.07547237711532316</v>
+        <v>0.07547237711532406</v>
       </c>
       <c r="D273">
-        <v>0.02087126888592612</v>
+        <v>0.02087126888592598</v>
       </c>
       <c r="E273">
         <v>2.1</v>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="C274">
-        <v>-0.07812721495493911</v>
+        <v>-0.07812721495493477</v>
       </c>
       <c r="D274">
-        <v>0.02160544258651712</v>
+        <v>0.02160544258651551</v>
       </c>
       <c r="E274">
         <v>2.2</v>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="C275">
-        <v>0.1769991640949968</v>
+        <v>0.1769991640949903</v>
       </c>
       <c r="D275">
-        <v>0.04894767181860507</v>
+        <v>0.04894767181860235</v>
       </c>
       <c r="E275">
         <v>4.9</v>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="C276">
-        <v>-0.01932140572428575</v>
+        <v>-0.01932140572427112</v>
       </c>
       <c r="D276">
-        <v>0.005343176795789113</v>
+        <v>0.005343176795784966</v>
       </c>
       <c r="E276">
         <v>0.5</v>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="C277">
-        <v>-0.1137181616638761</v>
+        <v>-0.1137181616638814</v>
       </c>
       <c r="D277">
-        <v>0.03144782793409716</v>
+        <v>0.031447827934098</v>
       </c>
       <c r="E277">
         <v>3.1</v>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="C278">
-        <v>0.04148594539104034</v>
+        <v>0.04148594539103969</v>
       </c>
       <c r="D278">
-        <v>0.01279660898890412</v>
+        <v>0.01279660898890392</v>
       </c>
       <c r="E278">
         <v>1.3</v>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="C279">
-        <v>-0.03075706340712749</v>
+        <v>-0.03075706340712689</v>
       </c>
       <c r="D279">
-        <v>0.009487215739163165</v>
+        <v>0.009487215739162985</v>
       </c>
       <c r="E279">
         <v>0.9</v>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="C280">
-        <v>-0.004566981106224568</v>
+        <v>-0.004566981106224339</v>
       </c>
       <c r="D280">
-        <v>0.001408714949730666</v>
+        <v>0.001408714949730597</v>
       </c>
       <c r="E280">
         <v>0.1</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="C281">
-        <v>-0.02562254407107431</v>
+        <v>-0.0256225440710747</v>
       </c>
       <c r="D281">
-        <v>0.007903439940633812</v>
+        <v>0.007903439940633935</v>
       </c>
       <c r="E281">
         <v>0.8</v>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="C282">
-        <v>-0.04287995580361465</v>
+        <v>-0.04287995580361477</v>
       </c>
       <c r="D282">
-        <v>0.01322660054406889</v>
+        <v>0.01322660054406893</v>
       </c>
       <c r="E282">
         <v>1.3</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="C283">
-        <v>0.05927140340635112</v>
+        <v>0.05927140340635111</v>
       </c>
       <c r="D283">
         <v>0.01828264889387048</v>
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="C284">
-        <v>0.0710806626170811</v>
+        <v>0.0710806626170806</v>
       </c>
       <c r="D284">
-        <v>0.02192529150798728</v>
+        <v>0.02192529150798713</v>
       </c>
       <c r="E284">
         <v>2.2</v>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="C285">
-        <v>-0.01216889588173064</v>
+        <v>-0.01216889588173045</v>
       </c>
       <c r="D285">
-        <v>0.003753574878368887</v>
+        <v>0.003753574878368832</v>
       </c>
       <c r="E285">
         <v>0.4</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="C286">
-        <v>-0.06001050173201519</v>
+        <v>-0.06001050173201523</v>
       </c>
       <c r="D286">
-        <v>0.01851062856719665</v>
+        <v>0.01851062856719668</v>
       </c>
       <c r="E286">
         <v>1.9</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="C287">
-        <v>0.03222402181002808</v>
+        <v>0.03222402181002736</v>
       </c>
       <c r="D287">
-        <v>0.009939708575181803</v>
+        <v>0.009939708575181585</v>
       </c>
       <c r="E287">
         <v>1</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="C289">
-        <v>0.3477497670590838</v>
+        <v>0.3477497670590843</v>
       </c>
       <c r="D289">
-        <v>0.1072656716170351</v>
+        <v>0.1072656716170353</v>
       </c>
       <c r="E289">
         <v>10.7</v>
@@ -6444,10 +6444,10 @@
         </is>
       </c>
       <c r="C290">
-        <v>0.07627240255209559</v>
+        <v>0.07627240255209444</v>
       </c>
       <c r="D290">
-        <v>0.02352671737147519</v>
+        <v>0.02352671737147484</v>
       </c>
       <c r="E290">
         <v>2.4</v>
@@ -6465,10 +6465,10 @@
         </is>
       </c>
       <c r="C291">
-        <v>-0.235293788517952</v>
+        <v>-0.2352937885179499</v>
       </c>
       <c r="D291">
-        <v>0.07257789549692659</v>
+        <v>0.07257789549692596</v>
       </c>
       <c r="E291">
         <v>7.3</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="C292">
-        <v>-0.2005870767454328</v>
+        <v>-0.2005870767454325</v>
       </c>
       <c r="D292">
-        <v>0.06187238509678415</v>
+        <v>0.06187238509678409</v>
       </c>
       <c r="E292">
         <v>6.2</v>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="C293">
-        <v>0.3495933502825804</v>
+        <v>0.3495933502825794</v>
       </c>
       <c r="D293">
-        <v>0.1078343368222563</v>
+        <v>0.107834336822256</v>
       </c>
       <c r="E293">
         <v>10.8</v>
@@ -6528,10 +6528,10 @@
         </is>
       </c>
       <c r="C294">
-        <v>-0.05398975755712477</v>
+        <v>-0.05398975755712482</v>
       </c>
       <c r="D294">
-        <v>0.01665349096789455</v>
+        <v>0.01665349096789457</v>
       </c>
       <c r="E294">
         <v>1.7</v>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="C295">
-        <v>0.504866001683607</v>
+        <v>0.5048660016836074</v>
       </c>
       <c r="D295">
-        <v>0.1557291934519059</v>
+        <v>0.1557291934519061</v>
       </c>
       <c r="E295">
         <v>15.6</v>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="C296">
-        <v>-0.4972124235711518</v>
+        <v>-0.4972124235711517</v>
       </c>
       <c r="D296">
         <v>0.1533683976318286</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="C297">
-        <v>-0.04371089719507517</v>
+        <v>-0.04371089719507561</v>
       </c>
       <c r="D297">
-        <v>0.0134829098068563</v>
+        <v>0.01348290980685644</v>
       </c>
       <c r="E297">
         <v>1.3</v>
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="C298">
-        <v>0.09357763119976081</v>
+        <v>0.09357763119976087</v>
       </c>
       <c r="D298">
-        <v>0.02886462741258466</v>
+        <v>0.0288646274125847</v>
       </c>
       <c r="E298">
         <v>2.9</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="C299">
-        <v>0.03521441271694341</v>
+        <v>0.03521441271694564</v>
       </c>
       <c r="D299">
-        <v>0.01086211405007389</v>
+        <v>0.01086211405007458</v>
       </c>
       <c r="E299">
         <v>1.1</v>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="C300">
-        <v>-0.08910288289258685</v>
+        <v>-0.08910288289258891</v>
       </c>
       <c r="D300">
-        <v>0.0274843622680658</v>
+        <v>0.02748436226806646</v>
       </c>
       <c r="E300">
         <v>2.7</v>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="C301">
-        <v>0.02728213472001408</v>
+        <v>0.0272821347200131</v>
       </c>
       <c r="D301">
-        <v>0.008908392016777114</v>
+        <v>0.008908392016776828</v>
       </c>
       <c r="E301">
         <v>0.9</v>
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="C302">
-        <v>-0.01320870606725201</v>
+        <v>-0.01320870606725127</v>
       </c>
       <c r="D302">
-        <v>0.004313017763787457</v>
+        <v>0.00431301776378723</v>
       </c>
       <c r="E302">
         <v>0.4</v>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="C303">
-        <v>-0.01391446796971139</v>
+        <v>-0.01391446796971127</v>
       </c>
       <c r="D303">
-        <v>0.00454346907421964</v>
+        <v>0.004543469074219614</v>
       </c>
       <c r="E303">
         <v>0.5</v>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="C304">
-        <v>0.08132224724501072</v>
+        <v>0.08132224724501039</v>
       </c>
       <c r="D304">
-        <v>0.02655402392732758</v>
+        <v>0.02655402392732756</v>
       </c>
       <c r="E304">
         <v>2.7</v>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="C305">
-        <v>0.03100956744124094</v>
+        <v>0.03100956744124066</v>
       </c>
       <c r="D305">
-        <v>0.01012550468914039</v>
+        <v>0.01012550468914033</v>
       </c>
       <c r="E305">
         <v>1</v>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="C306">
-        <v>-0.06448443647419458</v>
+        <v>-0.0644844364741943</v>
       </c>
       <c r="D306">
-        <v>0.02105600038224537</v>
+        <v>0.02105600038224535</v>
       </c>
       <c r="E306">
         <v>2.1</v>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="C307">
-        <v>-0.01161376918442952</v>
+        <v>-0.01161376918443071</v>
       </c>
       <c r="D307">
-        <v>0.00379222556259009</v>
+        <v>0.003792225562590493</v>
       </c>
       <c r="E307">
         <v>0.4</v>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="C308">
-        <v>-0.03861871942706159</v>
+        <v>-0.03861871942706054</v>
       </c>
       <c r="D308">
-        <v>0.01261010897324728</v>
+        <v>0.01261010897324698</v>
       </c>
       <c r="E308">
         <v>1.3</v>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="C309">
-        <v>0.03858592248395017</v>
+        <v>0.03858592248395012</v>
       </c>
       <c r="D309">
-        <v>0.01259939983962607</v>
+        <v>0.0125993998396261</v>
       </c>
       <c r="E309">
         <v>1.3</v>
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="C310">
-        <v>-0.02369082556505745</v>
+        <v>-0.02369082556505719</v>
       </c>
       <c r="D310">
-        <v>0.007735727555798394</v>
+        <v>0.007735727555798333</v>
       </c>
       <c r="E310">
         <v>0.8</v>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="C311">
-        <v>0.04080254014575693</v>
+        <v>0.04080254014575572</v>
       </c>
       <c r="D311">
-        <v>0.01332318847586503</v>
+        <v>0.01332318847586468</v>
       </c>
       <c r="E311">
         <v>1.3</v>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="C312">
-        <v>-0.08693157424706385</v>
+        <v>-0.08693157424706205</v>
       </c>
       <c r="D312">
-        <v>0.0283856285432202</v>
+        <v>0.02838562854321972</v>
       </c>
       <c r="E312">
         <v>2.8</v>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="C313">
-        <v>0.2271957460417405</v>
+        <v>0.2271957460417411</v>
       </c>
       <c r="D313">
-        <v>0.07418586525779451</v>
+        <v>0.07418586525779496</v>
       </c>
       <c r="E313">
         <v>7.4</v>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="C314">
-        <v>-0.7055055268648419</v>
+        <v>-0.7055055268648437</v>
       </c>
       <c r="D314">
-        <v>0.230367596517449</v>
+        <v>0.2303675965174504</v>
       </c>
       <c r="E314">
         <v>23</v>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="C315">
-        <v>0.05317090871024667</v>
+        <v>0.05317090871024557</v>
       </c>
       <c r="D315">
-        <v>0.0173618121726987</v>
+        <v>0.0173618121726984</v>
       </c>
       <c r="E315">
         <v>1.7</v>
@@ -6990,10 +6990,10 @@
         </is>
       </c>
       <c r="C316">
-        <v>0.3692859004231287</v>
+        <v>0.3692859004231308</v>
       </c>
       <c r="D316">
-        <v>0.1205823371594307</v>
+        <v>0.1205823371594318</v>
       </c>
       <c r="E316">
         <v>12.1</v>
@@ -7011,10 +7011,10 @@
         </is>
       </c>
       <c r="C317">
-        <v>0.02160807931250242</v>
+        <v>0.02160807931250197</v>
       </c>
       <c r="D317">
-        <v>0.007055651737698184</v>
+        <v>0.007055651737698063</v>
       </c>
       <c r="E317">
         <v>0.7</v>
@@ -7032,10 +7032,10 @@
         </is>
       </c>
       <c r="C318">
-        <v>-0.1865981464036233</v>
+        <v>-0.1865981464036226</v>
       </c>
       <c r="D318">
-        <v>0.06092959567962238</v>
+        <v>0.06092959567962233</v>
       </c>
       <c r="E318">
         <v>6.1</v>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="C319">
-        <v>0.1767329237386493</v>
+        <v>0.1767329237386487</v>
       </c>
       <c r="D319">
-        <v>0.0577083202283318</v>
+        <v>0.05770832022833181</v>
       </c>
       <c r="E319">
         <v>5.8</v>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="C320">
-        <v>0.1445481858691385</v>
+        <v>0.1445481858691386</v>
       </c>
       <c r="D320">
-        <v>0.04719908901012798</v>
+        <v>0.04719908901012819</v>
       </c>
       <c r="E320">
         <v>4.7</v>
@@ -7095,10 +7095,10 @@
         </is>
       </c>
       <c r="C321">
-        <v>-0.2831362037529943</v>
+        <v>-0.283136203752994</v>
       </c>
       <c r="D321">
-        <v>0.09245201385665069</v>
+        <v>0.09245201385665092</v>
       </c>
       <c r="E321">
         <v>9.199999999999999</v>
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="C322">
-        <v>-0.09218031881152962</v>
+        <v>-0.09218031881152686</v>
       </c>
       <c r="D322">
-        <v>0.0300994927498172</v>
+        <v>0.0300994927498164</v>
       </c>
       <c r="E322">
         <v>3</v>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="C323">
-        <v>0.3310938227121949</v>
+        <v>0.3310938227121921</v>
       </c>
       <c r="D323">
-        <v>0.108111538826534</v>
+        <v>0.1081115388265335</v>
       </c>
       <c r="E323">
         <v>10.8</v>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="C324">
-        <v>0.01247716859868766</v>
+        <v>0.01247716859868726</v>
       </c>
       <c r="D324">
-        <v>0.004955199436775501</v>
+        <v>0.004955199436775358</v>
       </c>
       <c r="E324">
         <v>0.5</v>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="C325">
-        <v>-0.02061098064107109</v>
+        <v>-0.02061098064107091</v>
       </c>
       <c r="D325">
-        <v>0.008185472437614442</v>
+        <v>0.008185472437614395</v>
       </c>
       <c r="E325">
         <v>0.8</v>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="C326">
-        <v>0.01190304833117103</v>
+        <v>0.01190304833117112</v>
       </c>
       <c r="D326">
-        <v>0.00472719254532907</v>
+        <v>0.004727192545329122</v>
       </c>
       <c r="E326">
         <v>0.5</v>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="C327">
-        <v>-0.01147883367393293</v>
+        <v>-0.01147883367393324</v>
       </c>
       <c r="D327">
-        <v>0.004558719368582926</v>
+        <v>0.004558719368583062</v>
       </c>
       <c r="E327">
         <v>0.5</v>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="C328">
-        <v>-0.03083239522768538</v>
+        <v>-0.03083239522768546</v>
       </c>
       <c r="D328">
-        <v>0.01224481870692487</v>
+        <v>0.01224481870692494</v>
       </c>
       <c r="E328">
         <v>1.2</v>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="C329">
-        <v>0.006878305749257573</v>
+        <v>0.006878305749257761</v>
       </c>
       <c r="D329">
-        <v>0.002731659551212259</v>
+        <v>0.002731659551212342</v>
       </c>
       <c r="E329">
         <v>0.3</v>
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="C330">
-        <v>0.02362063456591902</v>
+        <v>0.02362063456591881</v>
       </c>
       <c r="D330">
-        <v>0.009380730425461477</v>
+        <v>0.009380730425461423</v>
       </c>
       <c r="E330">
         <v>0.9</v>
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="C331">
-        <v>-0.006737445065051757</v>
+        <v>-0.006737445065051125</v>
       </c>
       <c r="D331">
-        <v>0.002675717950558254</v>
+        <v>0.002675717950558011</v>
       </c>
       <c r="E331">
         <v>0.3</v>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="C332">
-        <v>0.01061754462260772</v>
+        <v>0.01061754462260753</v>
       </c>
       <c r="D332">
-        <v>0.0042166658819869</v>
+        <v>0.004216665881986834</v>
       </c>
       <c r="E332">
         <v>0.4</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="C333">
-        <v>0.01388709543630675</v>
+        <v>0.01388709543630679</v>
       </c>
       <c r="D333">
-        <v>0.005515139668119303</v>
+        <v>0.005515139668119336</v>
       </c>
       <c r="E333">
         <v>0.6</v>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="C334">
-        <v>-0.006630340847993988</v>
+        <v>-0.006630340847993218</v>
       </c>
       <c r="D334">
-        <v>0.002633182438447216</v>
+        <v>0.002633182438446919</v>
       </c>
       <c r="E334">
         <v>0.3</v>
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="C335">
-        <v>0.04947259016240985</v>
+        <v>0.04947259016240947</v>
       </c>
       <c r="D335">
-        <v>0.01964761067141329</v>
+        <v>0.01964761067141321</v>
       </c>
       <c r="E335">
         <v>2</v>
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="C336">
-        <v>0.02158021602277604</v>
+        <v>0.02158021602277519</v>
       </c>
       <c r="D336">
-        <v>0.008570395874333281</v>
+        <v>0.00857039587433297</v>
       </c>
       <c r="E336">
         <v>0.9</v>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="C337">
-        <v>-0.1075113167748897</v>
+        <v>-0.1075113167748866</v>
       </c>
       <c r="D337">
-        <v>0.04269718823755889</v>
+        <v>0.04269718823755781</v>
       </c>
       <c r="E337">
         <v>4.3</v>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="C338">
-        <v>-0.150702000142337</v>
+        <v>-0.1507020001423367</v>
       </c>
       <c r="D338">
-        <v>0.0598499940366914</v>
+        <v>0.05984999403669148</v>
       </c>
       <c r="E338">
         <v>6</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="C339">
-        <v>0.189160729628796</v>
+        <v>0.1891607296287938</v>
       </c>
       <c r="D339">
-        <v>0.07512354533826211</v>
+        <v>0.07512354533826147</v>
       </c>
       <c r="E339">
         <v>7.5</v>
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="C340">
-        <v>0.003802949530646854</v>
+        <v>0.003802949530646494</v>
       </c>
       <c r="D340">
-        <v>0.001510308466484054</v>
+        <v>0.001510308466483915</v>
       </c>
       <c r="E340">
         <v>0.2</v>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="C341">
-        <v>-0.2169175799580841</v>
+        <v>-0.2169175799580842</v>
       </c>
       <c r="D341">
-        <v>0.0861469380279158</v>
+        <v>0.08614693802791613</v>
       </c>
       <c r="E341">
         <v>8.6</v>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="C342">
-        <v>0.2004322360269452</v>
+        <v>0.2004322360269457</v>
       </c>
       <c r="D342">
-        <v>0.07959992647505261</v>
+        <v>0.0795999264750531</v>
       </c>
       <c r="E342">
         <v>8</v>
@@ -7557,10 +7557,10 @@
         </is>
       </c>
       <c r="C343">
-        <v>0.01301034899542829</v>
+        <v>0.01301034899542718</v>
       </c>
       <c r="D343">
-        <v>0.005166947413147864</v>
+        <v>0.005166947413147441</v>
       </c>
       <c r="E343">
         <v>0.5</v>
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="C344">
-        <v>-0.1379046455457372</v>
+        <v>-0.1379046455457365</v>
       </c>
       <c r="D344">
-        <v>0.05476763550416687</v>
+        <v>0.05476763550416675</v>
       </c>
       <c r="E344">
         <v>5.5</v>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="C345">
-        <v>0.7031107042491248</v>
+        <v>0.7031107042491258</v>
       </c>
       <c r="D345">
-        <v>0.2792343261316946</v>
+        <v>0.2792343261316959</v>
       </c>
       <c r="E345">
         <v>27.9</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="C346">
-        <v>-0.5687161309369684</v>
+        <v>-0.5687161309369696</v>
       </c>
       <c r="D346">
-        <v>0.2258606854122669</v>
+        <v>0.2258606854122681</v>
       </c>
       <c r="E346">
         <v>22.6</v>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="C347">
-        <v>0.09597088981186994</v>
+        <v>0.09597088981187052</v>
       </c>
       <c r="D347">
-        <v>0.03113811823527537</v>
+        <v>0.03113811823527553</v>
       </c>
       <c r="E347">
         <v>3.1</v>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="C348">
-        <v>-0.1099847088438706</v>
+        <v>-0.109984708843871</v>
       </c>
       <c r="D348">
-        <v>0.03568495483126387</v>
+        <v>0.03568495483126394</v>
       </c>
       <c r="E348">
         <v>3.6</v>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="C349">
-        <v>0.005392779914455451</v>
+        <v>0.00539277991445514</v>
       </c>
       <c r="D349">
-        <v>0.001749707842891784</v>
+        <v>0.001749707842891682</v>
       </c>
       <c r="E349">
         <v>0.2</v>
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="C350">
-        <v>-0.025762031194964</v>
+        <v>-0.02576203119496397</v>
       </c>
       <c r="D350">
-        <v>0.008358588473047851</v>
+        <v>0.008358588473047832</v>
       </c>
       <c r="E350">
         <v>0.8</v>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="C351">
-        <v>0.01796229456385365</v>
+        <v>0.01796229456385373</v>
       </c>
       <c r="D351">
-        <v>0.005827934418473441</v>
+        <v>0.005827934418473463</v>
       </c>
       <c r="E351">
         <v>0.6</v>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="C352">
-        <v>-0.01173386090612187</v>
+        <v>-0.01173386090612206</v>
       </c>
       <c r="D352">
-        <v>0.003807095557489643</v>
+        <v>0.003807095557489702</v>
       </c>
       <c r="E352">
         <v>0.4</v>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="C353">
-        <v>0.1445125874364065</v>
+        <v>0.1445125874364073</v>
       </c>
       <c r="D353">
-        <v>0.04688765565163949</v>
+        <v>0.04688765565163971</v>
       </c>
       <c r="E353">
         <v>4.7</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="C354">
-        <v>-0.1592490887577383</v>
+        <v>-0.1592490887577386</v>
       </c>
       <c r="D354">
-        <v>0.05166896925014243</v>
+        <v>0.05166896925014249</v>
       </c>
       <c r="E354">
         <v>5.2</v>
@@ -7809,10 +7809,10 @@
         </is>
       </c>
       <c r="C355">
-        <v>0.01822768054855442</v>
+        <v>0.0182276805485543</v>
       </c>
       <c r="D355">
-        <v>0.00591403990510378</v>
+        <v>0.005914039905103736</v>
       </c>
       <c r="E355">
         <v>0.6</v>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="C356">
-        <v>-0.004947943355687589</v>
+        <v>-0.00494794335568785</v>
       </c>
       <c r="D356">
-        <v>0.001605378938685109</v>
+        <v>0.001605378938685193</v>
       </c>
       <c r="E356">
         <v>0.2</v>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="C357">
-        <v>-0.1075736708751134</v>
+        <v>-0.1075736708751138</v>
       </c>
       <c r="D357">
-        <v>0.03490268444189819</v>
+        <v>0.03490268444189831</v>
       </c>
       <c r="E357">
         <v>3.5</v>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="C358">
-        <v>0.06576987673881533</v>
+        <v>0.06576987673881578</v>
       </c>
       <c r="D358">
-        <v>0.02133928530023302</v>
+        <v>0.02133928530023315</v>
       </c>
       <c r="E358">
         <v>2.1</v>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="C359">
-        <v>-0.09036545255196821</v>
+        <v>-0.09036545255196832</v>
       </c>
       <c r="D359">
-        <v>0.02931941291221968</v>
+        <v>0.0293194129122197</v>
       </c>
       <c r="E359">
         <v>2.9</v>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="C360">
-        <v>0.2720470544867795</v>
+        <v>0.2720470544867787</v>
       </c>
       <c r="D360">
-        <v>0.08826669591970396</v>
+        <v>0.08826669591970367</v>
       </c>
       <c r="E360">
         <v>8.800000000000001</v>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="C361">
-        <v>-0.00747282854159138</v>
+        <v>-0.007472828541590796</v>
       </c>
       <c r="D361">
-        <v>0.002424587488311826</v>
+        <v>0.002424587488311635</v>
       </c>
       <c r="E361">
         <v>0.2</v>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="C362">
-        <v>-0.1488529742989051</v>
+        <v>-0.1488529742989052</v>
       </c>
       <c r="D362">
-        <v>0.04829591058786291</v>
+        <v>0.0482959105878629</v>
       </c>
       <c r="E362">
         <v>4.8</v>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="C363">
-        <v>0.01565850817463641</v>
+        <v>0.01565850817463643</v>
       </c>
       <c r="D363">
-        <v>0.005080462209797596</v>
+        <v>0.0050804622097976</v>
       </c>
       <c r="E363">
         <v>0.5</v>
@@ -7998,10 +7998,10 @@
         </is>
       </c>
       <c r="C364">
-        <v>0.1657231011045244</v>
+        <v>0.1657231011045243</v>
       </c>
       <c r="D364">
-        <v>0.05376948704575765</v>
+        <v>0.05376948704575757</v>
       </c>
       <c r="E364">
         <v>5.4</v>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="C365">
-        <v>-0.1232180802340822</v>
+        <v>-0.1232180802340819</v>
       </c>
       <c r="D365">
-        <v>0.03997857223761984</v>
+        <v>0.03997857223761974</v>
       </c>
       <c r="E365">
         <v>4</v>
@@ -8043,7 +8043,7 @@
         <v>0.2512264743557576</v>
       </c>
       <c r="D366">
-        <v>0.08151137993672555</v>
+        <v>0.08151137993672551</v>
       </c>
       <c r="E366">
         <v>8.199999999999999</v>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="C367">
-        <v>-0.769676818645312</v>
+        <v>-0.7696768186453121</v>
       </c>
       <c r="D367">
-        <v>0.2497245553199415</v>
+        <v>0.2497245553199413</v>
       </c>
       <c r="E367">
         <v>25</v>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="C368">
-        <v>0.2086551418574101</v>
+        <v>0.2086551418574102</v>
       </c>
       <c r="D368">
-        <v>0.06769895007007226</v>
+        <v>0.06769895007007225</v>
       </c>
       <c r="E368">
         <v>6.8</v>
@@ -8103,10 +8103,10 @@
         </is>
       </c>
       <c r="C369">
-        <v>0.2621192229590985</v>
+        <v>0.2621192229590986</v>
       </c>
       <c r="D369">
-        <v>0.08504557342584344</v>
+        <v>0.08504557342584342</v>
       </c>
       <c r="E369">
         <v>8.5</v>
@@ -8124,10 +8124,10 @@
         </is>
       </c>
       <c r="C370">
-        <v>-0.004775643646463247</v>
+        <v>-0.004775643646462518</v>
       </c>
       <c r="D370">
-        <v>0.00151983623513119</v>
+        <v>0.001519836235130958</v>
       </c>
       <c r="E370">
         <v>0.2</v>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="C371">
-        <v>0.009857941638024767</v>
+        <v>0.009857941638025317</v>
       </c>
       <c r="D371">
-        <v>0.003137264422225952</v>
+        <v>0.003137264422226127</v>
       </c>
       <c r="E371">
         <v>0.3</v>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="C372">
-        <v>-0.002182315565826049</v>
+        <v>-0.00218231556582561</v>
       </c>
       <c r="D372">
-        <v>0.0006945162828239052</v>
+        <v>0.0006945162828237653</v>
       </c>
       <c r="E372">
         <v>0.1</v>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="C373">
-        <v>0.0009956339801624999</v>
+        <v>0.0009956339801628243</v>
       </c>
       <c r="D373">
-        <v>0.0003168579383219902</v>
+        <v>0.0003168579383220933</v>
       </c>
       <c r="E373">
         <v>0</v>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="C374">
-        <v>-0.002369082470796063</v>
+        <v>-0.002369082470796785</v>
       </c>
       <c r="D374">
-        <v>0.0007539543671346869</v>
+        <v>0.0007539543671349164</v>
       </c>
       <c r="E374">
         <v>0.1</v>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="C375">
-        <v>-0.002682000993742112</v>
+        <v>-0.002682000993742418</v>
       </c>
       <c r="D375">
-        <v>0.0008535398774918815</v>
+        <v>0.0008535398774919785</v>
       </c>
       <c r="E375">
         <v>0.1</v>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="C376">
-        <v>-0.007020228838086544</v>
+        <v>-0.00702022883808699</v>
       </c>
       <c r="D376">
-        <v>0.002234169665263565</v>
+        <v>0.002234169665263706</v>
       </c>
       <c r="E376">
         <v>0.2</v>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="C377">
-        <v>0.01478546755177552</v>
+        <v>0.01478546755177526</v>
       </c>
       <c r="D377">
-        <v>0.004705436795977617</v>
+        <v>0.004705436795977532</v>
       </c>
       <c r="E377">
         <v>0.5</v>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="C378">
-        <v>-0.0006626120450868704</v>
+        <v>-0.0006626120450873977</v>
       </c>
       <c r="D378">
-        <v>0.0002108745690653068</v>
+        <v>0.0002108745690654745</v>
       </c>
       <c r="E378">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="C379">
-        <v>-0.4598506801821539</v>
+        <v>-0.4598506801821468</v>
       </c>
       <c r="D379">
-        <v>0.1463462892605382</v>
+        <v>0.1463462892605359</v>
       </c>
       <c r="E379">
         <v>14.6</v>
@@ -8334,10 +8334,10 @@
         </is>
       </c>
       <c r="C380">
-        <v>0.2127911104241401</v>
+        <v>0.2127911104241371</v>
       </c>
       <c r="D380">
-        <v>0.06772022036776552</v>
+        <v>0.06772022036776457</v>
       </c>
       <c r="E380">
         <v>6.8</v>
@@ -8355,10 +8355,10 @@
         </is>
       </c>
       <c r="C381">
-        <v>0.2570399001322325</v>
+        <v>0.2570399001322285</v>
       </c>
       <c r="D381">
-        <v>0.08180228321365307</v>
+        <v>0.08180228321365178</v>
       </c>
       <c r="E381">
         <v>8.199999999999999</v>
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="C382">
-        <v>-0.2675274798991646</v>
+        <v>-0.267527479899172</v>
       </c>
       <c r="D382">
-        <v>0.085139928341429</v>
+        <v>0.08513992834143133</v>
       </c>
       <c r="E382">
         <v>8.5</v>
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="C383">
-        <v>-0.002713460480573482</v>
+        <v>-0.002713460480573419</v>
       </c>
       <c r="D383">
-        <v>0.0008635517777852292</v>
+        <v>0.0008635517777852088</v>
       </c>
       <c r="E383">
         <v>0.1</v>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="C384">
-        <v>0.1374907486687509</v>
+        <v>0.1374907486687544</v>
       </c>
       <c r="D384">
-        <v>0.04375607505322085</v>
+        <v>0.04375607505322194</v>
       </c>
       <c r="E384">
         <v>4.4</v>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="C385">
-        <v>0.1325981185728458</v>
+        <v>0.1325981185728494</v>
       </c>
       <c r="D385">
-        <v>0.04219900818321749</v>
+        <v>0.0421990081832186</v>
       </c>
       <c r="E385">
         <v>4.2</v>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="C386">
-        <v>-0.5634691604685046</v>
+        <v>-0.5634691604685083</v>
       </c>
       <c r="D386">
-        <v>0.1793226025340488</v>
+        <v>0.1793226025340499</v>
       </c>
       <c r="E386">
         <v>17.9</v>
@@ -8481,10 +8481,10 @@
         </is>
       </c>
       <c r="C387">
-        <v>0.2546666596530759</v>
+        <v>0.2546666596530773</v>
       </c>
       <c r="D387">
-        <v>0.08104700557111508</v>
+        <v>0.08104700557111549</v>
       </c>
       <c r="E387">
         <v>8.1</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="C388">
-        <v>0.3211542389855117</v>
+        <v>0.3211542389855133</v>
       </c>
       <c r="D388">
-        <v>0.1022065056796358</v>
+        <v>0.1022065056796363</v>
       </c>
       <c r="E388">
         <v>10.2</v>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="C389">
-        <v>-0.2278649525305643</v>
+        <v>-0.2278649525305608</v>
       </c>
       <c r="D389">
-        <v>0.07251743161968889</v>
+        <v>0.07251743161968777</v>
       </c>
       <c r="E389">
         <v>7.3</v>
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="C390">
-        <v>-0.01353777040083388</v>
+        <v>-0.01353777040083354</v>
       </c>
       <c r="D390">
-        <v>0.004308360405682997</v>
+        <v>0.004308360405682888</v>
       </c>
       <c r="E390">
         <v>0.4</v>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="C391">
-        <v>0.1028705983627382</v>
+        <v>0.1028705983627365</v>
       </c>
       <c r="D391">
-        <v>0.0327383017862114</v>
+        <v>0.03273830178621084</v>
       </c>
       <c r="E391">
         <v>3.3</v>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="C392">
-        <v>0.1433035563294455</v>
+        <v>0.1433035563294437</v>
       </c>
       <c r="D392">
-        <v>0.04560598605257156</v>
+        <v>0.04560598605257098</v>
       </c>
       <c r="E392">
         <v>4.6</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="C393">
-        <v>0.002508766733214536</v>
+        <v>0.002508766733214069</v>
       </c>
       <c r="D393">
-        <v>0.001075538544528767</v>
+        <v>0.001075538544528564</v>
       </c>
       <c r="E393">
         <v>0.1</v>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="C394">
-        <v>-0.001371552749148794</v>
+        <v>-0.001371552749150217</v>
       </c>
       <c r="D394">
-        <v>0.0005880011991683948</v>
+        <v>0.0005880011991690027</v>
       </c>
       <c r="E394">
         <v>0.1</v>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="C395">
-        <v>-0.0009715497077117813</v>
+        <v>-0.0009715497077122425</v>
       </c>
       <c r="D395">
-        <v>0.0004165150728185779</v>
+        <v>0.0004165150728187744</v>
       </c>
       <c r="E395">
         <v>0</v>
@@ -8670,10 +8670,10 @@
         </is>
       </c>
       <c r="C396">
-        <v>0.0007945698508513157</v>
+        <v>0.000794569850852242</v>
       </c>
       <c r="D396">
-        <v>0.0003406416744916171</v>
+        <v>0.0003406416744920133</v>
       </c>
       <c r="E396">
         <v>0</v>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="C397">
-        <v>-0.004358768564715709</v>
+        <v>-0.004358768564715415</v>
       </c>
       <c r="D397">
-        <v>0.001868656633542495</v>
+        <v>0.001868656633542363</v>
       </c>
       <c r="E397">
         <v>0.2</v>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="C398">
-        <v>0.001363306028463665</v>
+        <v>0.001363306028463599</v>
       </c>
       <c r="D398">
-        <v>0.0005844657305872028</v>
+        <v>0.0005844657305871731</v>
       </c>
       <c r="E398">
         <v>0.1</v>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="C399">
-        <v>0.002904847387106465</v>
+        <v>0.002904847387107622</v>
       </c>
       <c r="D399">
-        <v>0.001245343096049221</v>
+        <v>0.001245343096049713</v>
       </c>
       <c r="E399">
         <v>0.1</v>
@@ -8754,10 +8754,10 @@
         </is>
       </c>
       <c r="C400">
-        <v>0.001109099049376965</v>
+        <v>0.001109099049377536</v>
       </c>
       <c r="D400">
-        <v>0.0004754841339021898</v>
+        <v>0.0004754841339024334</v>
       </c>
       <c r="E400">
         <v>0</v>
@@ -8775,10 +8775,10 @@
         </is>
       </c>
       <c r="C401">
-        <v>-0.002606537861852015</v>
+        <v>-0.002606537861851573</v>
       </c>
       <c r="D401">
-        <v>0.001117454206116383</v>
+        <v>0.00111745420611619</v>
       </c>
       <c r="E401">
         <v>0.1</v>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="C402">
-        <v>0.3717705871774306</v>
+        <v>0.371770587177447</v>
       </c>
       <c r="D402">
-        <v>0.1593825328347996</v>
+        <v>0.1593825328348062</v>
       </c>
       <c r="E402">
         <v>15.9</v>
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="C403">
-        <v>-0.1711957080643945</v>
+        <v>-0.1711957080644019</v>
       </c>
       <c r="D403">
-        <v>0.07339366400367721</v>
+        <v>0.07339366400368018</v>
       </c>
       <c r="E403">
         <v>7.3</v>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="C404">
-        <v>-0.207433487958824</v>
+        <v>-0.2074334879588332</v>
       </c>
       <c r="D404">
-        <v>0.08892923713154184</v>
+        <v>0.08892923713154553</v>
       </c>
       <c r="E404">
         <v>8.9</v>
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="C405">
-        <v>-0.7161891708588141</v>
+        <v>-0.7161891708588057</v>
       </c>
       <c r="D405">
-        <v>0.3070389320117322</v>
+        <v>0.3070389320117277</v>
       </c>
       <c r="E405">
         <v>30.7</v>
@@ -8880,10 +8880,10 @@
         </is>
       </c>
       <c r="C406">
-        <v>-0.01099114226384047</v>
+        <v>-0.0109911422638403</v>
       </c>
       <c r="D406">
-        <v>0.004712035199068743</v>
+        <v>0.004712035199068656</v>
       </c>
       <c r="E406">
         <v>0.5</v>
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="C407">
-        <v>0.3709144992938329</v>
+        <v>0.3709144992938277</v>
       </c>
       <c r="D407">
-        <v>0.1590155176380007</v>
+        <v>0.159015517637998</v>
       </c>
       <c r="E407">
         <v>15.9</v>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="C408">
-        <v>0.3701425496923207</v>
+        <v>0.3701425496923161</v>
       </c>
       <c r="D408">
-        <v>0.1586845735371133</v>
+        <v>0.1586845735371109</v>
       </c>
       <c r="E408">
         <v>15.9</v>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="C409">
-        <v>0.03009037399257279</v>
+        <v>0.03009037399257073</v>
       </c>
       <c r="D409">
-        <v>0.01290010610385851</v>
+        <v>0.01290010610385759</v>
       </c>
       <c r="E409">
         <v>1.3</v>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="C410">
-        <v>-0.01714427778645934</v>
+        <v>-0.01714427778645885</v>
       </c>
       <c r="D410">
-        <v>0.007349958580572633</v>
+        <v>0.0073499585805724</v>
       </c>
       <c r="E410">
         <v>0.7</v>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="C411">
-        <v>-0.01655967756674421</v>
+        <v>-0.01655967756674279</v>
       </c>
       <c r="D411">
-        <v>0.007099333418368744</v>
+        <v>0.007099333418368116</v>
       </c>
       <c r="E411">
         <v>0.7</v>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="C412">
-        <v>0.00840240820777375</v>
+        <v>0.008402408207769711</v>
       </c>
       <c r="D412">
-        <v>0.003602213699137384</v>
+        <v>0.003602213699135643</v>
       </c>
       <c r="E412">
         <v>0.4</v>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="C413">
-        <v>0.006045837202109183</v>
+        <v>0.006045837202109478</v>
       </c>
       <c r="D413">
-        <v>0.002591923297899663</v>
+        <v>0.002591923297899782</v>
       </c>
       <c r="E413">
         <v>0.3</v>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="C414">
-        <v>-0.004680214034655364</v>
+        <v>-0.004680214034653608</v>
       </c>
       <c r="D414">
-        <v>0.002006464181891669</v>
+        <v>0.00200646418189091</v>
       </c>
       <c r="E414">
         <v>0.2</v>
@@ -9069,10 +9069,10 @@
         </is>
       </c>
       <c r="C415">
-        <v>-0.01301901355798362</v>
+        <v>-0.01301901355798161</v>
       </c>
       <c r="D415">
-        <v>0.005581408071133161</v>
+        <v>0.005581408071132284</v>
       </c>
       <c r="E415">
         <v>0.6</v>
@@ -9090,10 +9090,10 @@
         </is>
       </c>
       <c r="C416">
-        <v>-0.001652095533513949</v>
+        <v>-0.001652095533514455</v>
       </c>
       <c r="D416">
-        <v>0.0005367926480566391</v>
+        <v>0.0005367926480568011</v>
       </c>
       <c r="E416">
         <v>0.1</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="C417">
-        <v>0.001755079014256331</v>
+        <v>0.00175507901425554</v>
       </c>
       <c r="D417">
-        <v>0.0005702536521041549</v>
+        <v>0.0005702536521038955</v>
       </c>
       <c r="E417">
         <v>0.1</v>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="C418">
-        <v>-0.0003061897293014255</v>
+        <v>-0.0003061897293013425</v>
       </c>
       <c r="D418">
-        <v>9.94860117137832E-05</v>
+        <v>9.948601171375582E-05</v>
       </c>
       <c r="E418">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="C419">
-        <v>0.0001296842846216886</v>
+        <v>0.0001296842846218713</v>
       </c>
       <c r="D419">
-        <v>4.213652851257425E-05</v>
+        <v>4.213652851263344E-05</v>
       </c>
       <c r="E419">
         <v>0</v>
@@ -9174,10 +9174,10 @@
         </is>
       </c>
       <c r="C420">
-        <v>-0.001805834545508953</v>
+        <v>-0.001805834545508901</v>
       </c>
       <c r="D420">
-        <v>0.0005867449478385285</v>
+        <v>0.0005867449478385091</v>
       </c>
       <c r="E420">
         <v>0.1</v>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="C421">
-        <v>0.001588557414372004</v>
+        <v>0.001588557414372407</v>
       </c>
       <c r="D421">
-        <v>0.0005161480820888352</v>
+        <v>0.000516148082088964</v>
       </c>
       <c r="E421">
         <v>0.1</v>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="C422">
-        <v>-0.00230065572035031</v>
+        <v>-0.00230065572034987</v>
       </c>
       <c r="D422">
-        <v>0.0007475203772064856</v>
+        <v>0.0007475203772063394</v>
       </c>
       <c r="E422">
         <v>0.1</v>
@@ -9237,10 +9237,10 @@
         </is>
       </c>
       <c r="C423">
-        <v>0.003567363388828786</v>
+        <v>0.003567363388829512</v>
       </c>
       <c r="D423">
-        <v>0.001159094254069383</v>
+        <v>0.001159094254069614</v>
       </c>
       <c r="E423">
         <v>0.1</v>
@@ -9258,10 +9258,10 @@
         </is>
       </c>
       <c r="C424">
-        <v>-0.001866899786044031</v>
+        <v>-0.001866899786043976</v>
       </c>
       <c r="D424">
-        <v>0.0006065860354185665</v>
+        <v>0.0006065860354185465</v>
       </c>
       <c r="E424">
         <v>0.1</v>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="C425">
-        <v>-0.4672898472780427</v>
+        <v>-0.4672898472780355</v>
       </c>
       <c r="D425">
-        <v>0.151830054280723</v>
+        <v>0.1518300542807201</v>
       </c>
       <c r="E425">
         <v>15.2</v>
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="C426">
-        <v>0.2162942664312201</v>
+        <v>0.2162942664312168</v>
       </c>
       <c r="D426">
-        <v>0.07027751705746169</v>
+        <v>0.07027751705746034</v>
       </c>
       <c r="E426">
         <v>7</v>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="C427">
-        <v>0.262166803826063</v>
+        <v>0.2621668038260584</v>
       </c>
       <c r="D427">
-        <v>0.08518224884913989</v>
+        <v>0.08518224884913807</v>
       </c>
       <c r="E427">
         <v>8.5</v>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="C428">
-        <v>-0.2208388158334039</v>
+        <v>-0.2208388158334174</v>
       </c>
       <c r="D428">
-        <v>0.07175411490446015</v>
+        <v>0.07175411490446425</v>
       </c>
       <c r="E428">
         <v>7.2</v>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="C429">
-        <v>-0.005035636605121583</v>
+        <v>-0.00503563660512166</v>
       </c>
       <c r="D429">
-        <v>0.001636160048302276</v>
+        <v>0.001636160048302295</v>
       </c>
       <c r="E429">
         <v>0.2</v>
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="C430">
-        <v>0.1160132464358638</v>
+        <v>0.1160132464358704</v>
       </c>
       <c r="D430">
-        <v>0.03769458636057076</v>
+        <v>0.03769458636057273</v>
       </c>
       <c r="E430">
         <v>3.8</v>
@@ -9405,10 +9405,10 @@
         </is>
       </c>
       <c r="C431">
-        <v>0.1131186229164768</v>
+        <v>0.1131186229164837</v>
       </c>
       <c r="D431">
-        <v>0.03675407620690315</v>
+        <v>0.03675407620690523</v>
       </c>
       <c r="E431">
         <v>3.7</v>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="C432">
-        <v>0.2516031355805532</v>
+        <v>0.2516031355805517</v>
       </c>
       <c r="D432">
-        <v>0.08174994161528515</v>
+        <v>0.08174994161528433</v>
       </c>
       <c r="E432">
         <v>8.199999999999999</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="C433">
-        <v>-0.1110625145929103</v>
+        <v>-0.1110625145929097</v>
       </c>
       <c r="D433">
-        <v>0.03608601324728057</v>
+        <v>0.03608601324728024</v>
       </c>
       <c r="E433">
         <v>3.6</v>
@@ -9468,10 +9468,10 @@
         </is>
       </c>
       <c r="C434">
-        <v>-0.1429485697291564</v>
+        <v>-0.1429485697291551</v>
       </c>
       <c r="D434">
-        <v>0.04644630998887395</v>
+        <v>0.04644630998887334</v>
       </c>
       <c r="E434">
         <v>4.6</v>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="C435">
-        <v>0.5701456514478119</v>
+        <v>0.5701456514478138</v>
       </c>
       <c r="D435">
-        <v>0.1852495741379379</v>
+        <v>0.1852495741379378</v>
       </c>
       <c r="E435">
         <v>18.5</v>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="C436">
-        <v>0.005433385089086835</v>
+        <v>0.005433385089086781</v>
       </c>
       <c r="D436">
-        <v>0.001765394985167033</v>
+        <v>0.001765394985167008</v>
       </c>
       <c r="E436">
         <v>0.2</v>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="C437">
-        <v>-0.2657711396425332</v>
+        <v>-0.2657711396425338</v>
       </c>
       <c r="D437">
-        <v>0.08635335604491642</v>
+        <v>0.08635335604491627</v>
       </c>
       <c r="E437">
         <v>8.6</v>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="C438">
-        <v>-0.3150223999412863</v>
+        <v>-0.3150223999412876</v>
       </c>
       <c r="D438">
         <v>0.102355889735969</v>
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="C439">
-        <v>0.001304446272471429</v>
+        <v>0.001304446272466925</v>
       </c>
       <c r="D439">
-        <v>0.0004336760750005718</v>
+        <v>0.0004336760749990725</v>
       </c>
       <c r="E439">
         <v>0</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="C440">
-        <v>-0.001808341252579002</v>
+        <v>-0.001808341252578219</v>
       </c>
       <c r="D440">
-        <v>0.0006012009488089176</v>
+        <v>0.0006012009488086549</v>
       </c>
       <c r="E440">
         <v>0.1</v>
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="C441">
-        <v>0.0008977727588107046</v>
+        <v>0.0008977727588118576</v>
       </c>
       <c r="D441">
-        <v>0.0002984734400335289</v>
+        <v>0.0002984734400339109</v>
       </c>
       <c r="E441">
         <v>0</v>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="C442">
-        <v>-0.0008454084761056645</v>
+        <v>-0.0008454084761036985</v>
       </c>
       <c r="D442">
-        <v>0.0002810644159341944</v>
+        <v>0.0002810644159335396</v>
       </c>
       <c r="E442">
         <v>0</v>
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="C443">
-        <v>-0.000434425990703699</v>
+        <v>-0.0004344259907040186</v>
       </c>
       <c r="D443">
-        <v>0.0001444292206605554</v>
+        <v>0.0001444292206606611</v>
       </c>
       <c r="E443">
         <v>0</v>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="C444">
-        <v>-0.0002987686904954666</v>
+        <v>-0.0002987686904961222</v>
       </c>
       <c r="D444">
-        <v>9.932860843831535E-05</v>
+        <v>9.93286084385329E-05</v>
       </c>
       <c r="E444">
         <v>0</v>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="C445">
-        <v>0.002259811552092358</v>
+        <v>0.002259811552095835</v>
       </c>
       <c r="D445">
-        <v>0.0007512967186418397</v>
+        <v>0.0007512967186429927</v>
       </c>
       <c r="E445">
         <v>0.1</v>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="C446">
-        <v>-0.002128164227264948</v>
+        <v>-0.002128164227265663</v>
       </c>
       <c r="D446">
-        <v>0.0007075292624266381</v>
+        <v>0.0007075292624268726</v>
       </c>
       <c r="E446">
         <v>0.1</v>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="C447">
-        <v>0.001540104012741737</v>
+        <v>0.001540104012740894</v>
       </c>
       <c r="D447">
-        <v>0.0005120228233494347</v>
+        <v>0.0005120228233491524</v>
       </c>
       <c r="E447">
         <v>0.1</v>
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="C448">
-        <v>0.2942269337440006</v>
+        <v>0.2942269337440026</v>
       </c>
       <c r="D448">
-        <v>0.09781865645090891</v>
+        <v>0.09781865645090919</v>
       </c>
       <c r="E448">
         <v>9.800000000000001</v>
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="C449">
-        <v>-0.1352789206782845</v>
+        <v>-0.1352789206782856</v>
       </c>
       <c r="D449">
-        <v>0.04497481620221892</v>
+        <v>0.04497481620221909</v>
       </c>
       <c r="E449">
         <v>4.5</v>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="C450">
-        <v>-0.1654315878201132</v>
+        <v>-0.165431587820114</v>
       </c>
       <c r="D450">
-        <v>0.05499936885174432</v>
+        <v>0.05499936885174434</v>
       </c>
       <c r="E450">
         <v>5.5</v>
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="C451">
-        <v>0.1385784466257056</v>
+        <v>0.1385784466257139</v>
       </c>
       <c r="D451">
-        <v>0.04607177626292659</v>
+        <v>0.04607177626292915</v>
       </c>
       <c r="E451">
         <v>4.6</v>
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="C452">
-        <v>0.0002015986163271045</v>
+        <v>0.0002015986163273986</v>
       </c>
       <c r="D452">
-        <v>6.702345546868798E-05</v>
+        <v>6.702345546878549E-05</v>
       </c>
       <c r="E452">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="C453">
-        <v>-0.07218240206431939</v>
+        <v>-0.07218240206432362</v>
       </c>
       <c r="D453">
-        <v>0.02399775404475529</v>
+        <v>0.0239977540447566</v>
       </c>
       <c r="E453">
         <v>2.4</v>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="C454">
-        <v>-0.06893225841775151</v>
+        <v>-0.06893225841775574</v>
       </c>
       <c r="D454">
-        <v>0.02291721161876398</v>
+        <v>0.02291721161876529</v>
       </c>
       <c r="E454">
         <v>2.3</v>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="C455">
-        <v>-0.5238491452161413</v>
+        <v>-0.5238491452161383</v>
       </c>
       <c r="D455">
-        <v>0.1741588335097309</v>
+        <v>0.1741588335097292</v>
       </c>
       <c r="E455">
         <v>17.4</v>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="C456">
-        <v>0.2425231791243971</v>
+        <v>0.2425231791243958</v>
       </c>
       <c r="D456">
-        <v>0.08062923145164093</v>
+        <v>0.08062923145164017</v>
       </c>
       <c r="E456">
         <v>8.1</v>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="C457">
-        <v>0.2889250767859368</v>
+        <v>0.2889250767859345</v>
       </c>
       <c r="D457">
-        <v>0.09605600162616762</v>
+        <v>0.09605600162616645</v>
       </c>
       <c r="E457">
         <v>9.6</v>
@@ -9972,10 +9972,10 @@
         </is>
       </c>
       <c r="C458">
-        <v>0.5262696768293011</v>
+        <v>0.5262696768293013</v>
       </c>
       <c r="D458">
-        <v>0.1749635632035198</v>
+        <v>0.1749635632035191</v>
       </c>
       <c r="E458">
         <v>17.5</v>
@@ -9993,10 +9993,10 @@
         </is>
       </c>
       <c r="C459">
-        <v>0.003530655925490532</v>
+        <v>0.003530655925490591</v>
       </c>
       <c r="D459">
-        <v>0.001173801509695971</v>
+        <v>0.001173801509695985</v>
       </c>
       <c r="E459">
         <v>0.1</v>
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="C460">
-        <v>-0.2457289870842238</v>
+        <v>-0.2457289870842237</v>
       </c>
       <c r="D460">
-        <v>0.08169503403973005</v>
+        <v>0.08169503403972966</v>
       </c>
       <c r="E460">
         <v>8.199999999999999</v>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="C461">
-        <v>-0.290705455822345</v>
+        <v>-0.2907054558223451</v>
       </c>
       <c r="D461">
-        <v>0.09664790625943394</v>
+        <v>0.09664790625943356</v>
       </c>
       <c r="E461">
         <v>9.699999999999999</v>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="C462">
-        <v>0.5206153787424264</v>
+        <v>0.5206153799775478</v>
       </c>
       <c r="D462">
-        <v>0.2101612629053792</v>
+        <v>0.2101612633268587</v>
       </c>
       <c r="E462">
         <v>21</v>
@@ -10077,10 +10077,10 @@
         </is>
       </c>
       <c r="C463">
-        <v>0.5355924075898625</v>
+        <v>0.5355924063903477</v>
       </c>
       <c r="D463">
-        <v>0.2162071682429254</v>
+        <v>0.2162071676793761</v>
       </c>
       <c r="E463">
         <v>21.6</v>
@@ -10098,10 +10098,10 @@
         </is>
       </c>
       <c r="C464">
-        <v>0.05687982479773743</v>
+        <v>0.05687982518697059</v>
       </c>
       <c r="D464">
-        <v>0.02296116538509592</v>
+        <v>0.02296116553379607</v>
       </c>
       <c r="E464">
         <v>2.3</v>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="C465">
-        <v>-0.2298851433632353</v>
+        <v>-0.2298851439086207</v>
       </c>
       <c r="D465">
-        <v>0.09279970209313475</v>
+        <v>0.09279970227924499</v>
       </c>
       <c r="E465">
         <v>9.300000000000001</v>
@@ -10140,10 +10140,10 @@
         </is>
       </c>
       <c r="C466">
-        <v>-0.270535856349696</v>
+        <v>-0.270535855743803</v>
       </c>
       <c r="D466">
-        <v>0.1092095231012564</v>
+        <v>0.1092095228165992</v>
       </c>
       <c r="E466">
         <v>10.9</v>
@@ -10161,10 +10161,10 @@
         </is>
       </c>
       <c r="C467">
-        <v>-0.03634215477788555</v>
+        <v>-0.036342155026578</v>
       </c>
       <c r="D467">
-        <v>0.01467054846376702</v>
+        <v>0.0146705485587759</v>
       </c>
       <c r="E467">
         <v>1.5</v>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="C468">
-        <v>-0.3867223350833026</v>
+        <v>-0.3867223360007727</v>
       </c>
       <c r="D468">
-        <v>0.1561115127469838</v>
+        <v>0.1561115130600663</v>
       </c>
       <c r="E468">
         <v>15.6</v>
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="C469">
-        <v>-0.4004190612748895</v>
+        <v>-0.4004190603781093</v>
       </c>
       <c r="D469">
-        <v>0.161640587360658</v>
+        <v>0.1616405869393377</v>
       </c>
       <c r="E469">
         <v>16.2</v>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="C470">
-        <v>-0.04022332495759914</v>
+        <v>-0.04022332523285102</v>
       </c>
       <c r="D470">
-        <v>0.01623729362694219</v>
+        <v>0.01623729373209767</v>
       </c>
       <c r="E470">
         <v>1.6</v>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="C471">
-        <v>-4.476767025574603E-07</v>
+        <v>-4.476767006128535E-07</v>
       </c>
       <c r="D471">
-        <v>1.807174836249694E-07</v>
+        <v>1.807174827736643E-07</v>
       </c>
       <c r="E471">
         <v>0</v>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="C472">
-        <v>1.952164985972368E-07</v>
+        <v>1.952164975713155E-07</v>
       </c>
       <c r="D472">
-        <v>7.880471372986367E-08</v>
+        <v>7.880471328680619E-08</v>
       </c>
       <c r="E472">
         <v>0</v>
@@ -10287,10 +10287,10 @@
         </is>
       </c>
       <c r="C473">
-        <v>2.705101370647557E-07</v>
+        <v>2.705101362146523E-07</v>
       </c>
       <c r="D473">
-        <v>1.091991407775203E-07</v>
+        <v>1.091991403942844E-07</v>
       </c>
       <c r="E473">
         <v>0</v>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="C474">
-        <v>3.358303505749867E-07</v>
+        <v>3.358303488840142E-07</v>
       </c>
       <c r="D474">
-        <v>1.355675100671854E-07</v>
+        <v>1.355675093348336E-07</v>
       </c>
       <c r="E474">
         <v>0</v>
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="C475">
-        <v>1.869197285828327E-08</v>
+        <v>1.869197296250347E-08</v>
       </c>
       <c r="D475">
-        <v>7.545548561356306E-09</v>
+        <v>7.545548600659144E-09</v>
       </c>
       <c r="E475">
         <v>0</v>
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="C476">
-        <v>-1.857742416274859E-07</v>
+        <v>-1.857742410044105E-07</v>
       </c>
       <c r="D476">
-        <v>7.499307709662905E-08</v>
+        <v>7.499307681759035E-08</v>
       </c>
       <c r="E476">
         <v>0</v>
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="C477">
-        <v>-1.75124161814618E-07</v>
+        <v>-1.75124160825546E-07</v>
       </c>
       <c r="D477">
-        <v>7.069386828546794E-08</v>
+        <v>7.069386786026177E-08</v>
       </c>
       <c r="E477">
         <v>0</v>
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="C478">
-        <v>4.179340017002102E-07</v>
+        <v>4.179339984436425E-07</v>
       </c>
       <c r="D478">
-        <v>1.687109931723139E-07</v>
+        <v>1.687109917958037E-07</v>
       </c>
       <c r="E478">
         <v>0</v>
@@ -10413,10 +10413,10 @@
         </is>
       </c>
       <c r="C479">
-        <v>-1.595525608325778E-07</v>
+        <v>-1.595525593520164E-07</v>
       </c>
       <c r="D479">
-        <v>6.440794692880497E-08</v>
+        <v>6.440794630750146E-08</v>
       </c>
       <c r="E479">
         <v>0</v>
@@ -10434,10 +10434,10 @@
         </is>
       </c>
       <c r="C480">
-        <v>-2.690458749611076E-07</v>
+        <v>-2.69045873212137E-07</v>
       </c>
       <c r="D480">
-        <v>1.086080495698989E-07</v>
+        <v>1.086080488240264E-07</v>
       </c>
       <c r="E480">
         <v>0</v>
@@ -10455,10 +10455,10 @@
         </is>
       </c>
       <c r="C481">
-        <v>-2.38796424376415E-07</v>
+        <v>-2.387964194439096E-07</v>
       </c>
       <c r="D481">
-        <v>9.639699512039497E-08</v>
+        <v>9.639699309387828E-08</v>
       </c>
       <c r="E481">
         <v>0</v>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="C482">
-        <v>-6.158563503893069E-08</v>
+        <v>-6.158563486263757E-08</v>
       </c>
       <c r="D482">
-        <v>2.486080005526485E-08</v>
+        <v>2.486079997497716E-08</v>
       </c>
       <c r="E482">
         <v>0</v>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="C483">
-        <v>1.524718128032975E-07</v>
+        <v>1.524718105314071E-07</v>
       </c>
       <c r="D483">
-        <v>6.154960080821417E-08</v>
+        <v>6.154959986851691E-08</v>
       </c>
       <c r="E483">
         <v>0</v>
@@ -10518,10 +10518,10 @@
         </is>
       </c>
       <c r="C484">
-        <v>1.338147127568537E-07</v>
+        <v>1.33814709944724E-07</v>
       </c>
       <c r="D484">
-        <v>5.401812965308998E-08</v>
+        <v>5.401812849807315E-08</v>
       </c>
       <c r="E484">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         </is>
       </c>
       <c r="C485">
-        <v>-0.5477781759035103</v>
+        <v>-0.5477781751793301</v>
       </c>
       <c r="D485">
-        <v>0.231916350522638</v>
+        <v>0.2319163481030391</v>
       </c>
       <c r="E485">
         <v>23.2</v>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="C486">
-        <v>0.5121454116650695</v>
+        <v>0.5121454123166354</v>
       </c>
       <c r="D486">
-        <v>0.2168302791807443</v>
+        <v>0.2168302774810535</v>
       </c>
       <c r="E486">
         <v>21.7</v>
@@ -10581,10 +10581,10 @@
         </is>
       </c>
       <c r="C487">
-        <v>0.004976450702745934</v>
+        <v>0.004976459924040222</v>
       </c>
       <c r="D487">
-        <v>0.002106911768861615</v>
+        <v>0.002106915653743784</v>
       </c>
       <c r="E487">
         <v>0.2</v>
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="C488">
-        <v>0.2418792651368277</v>
+        <v>0.2418792648170559</v>
       </c>
       <c r="D488">
-        <v>0.1024059718062075</v>
+        <v>0.1024059707377991</v>
       </c>
       <c r="E488">
         <v>10.2</v>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="C489">
-        <v>-0.2586924161417106</v>
+        <v>-0.258692416470826</v>
       </c>
       <c r="D489">
-        <v>0.10952426310251</v>
+        <v>0.1095242622439703</v>
       </c>
       <c r="E489">
         <v>11</v>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="C490">
-        <v>-0.003179583920044169</v>
+        <v>-0.003179589811795266</v>
       </c>
       <c r="D490">
-        <v>0.001346160784337267</v>
+        <v>0.001346163266500678</v>
       </c>
       <c r="E490">
         <v>0.1</v>
@@ -10665,10 +10665,10 @@
         </is>
       </c>
       <c r="C491">
-        <v>0.4068993216004409</v>
+        <v>0.4068993210625073</v>
       </c>
       <c r="D491">
-        <v>0.1722715687605887</v>
+        <v>0.172271566963268</v>
       </c>
       <c r="E491">
         <v>17.2</v>
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="C492">
-        <v>-0.3828896512679049</v>
+        <v>-0.3828896517550279</v>
       </c>
       <c r="D492">
-        <v>0.1621064410397022</v>
+        <v>0.1621064397689811</v>
       </c>
       <c r="E492">
         <v>16.2</v>
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="C493">
-        <v>-0.003519155611933876</v>
+        <v>-0.003519162132894479</v>
       </c>
       <c r="D493">
-        <v>0.001489927423805814</v>
+        <v>0.001489930171051813</v>
       </c>
       <c r="E493">
         <v>0.1</v>
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="C494">
-        <v>-1.705749270382435E-07</v>
+        <v>-1.705749347463703E-07</v>
       </c>
       <c r="D494">
-        <v>7.221739804461087E-08</v>
+        <v>7.221740065007452E-08</v>
       </c>
       <c r="E494">
         <v>0</v>
@@ -10749,10 +10749,10 @@
         </is>
       </c>
       <c r="C495">
-        <v>9.141066345394667E-08</v>
+        <v>9.141066700801836E-08</v>
       </c>
       <c r="D495">
-        <v>3.870111734941892E-08</v>
+        <v>3.870111850152171E-08</v>
       </c>
       <c r="E495">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         </is>
       </c>
       <c r="C496">
-        <v>8.51826188676376E-08</v>
+        <v>8.51826232051156E-08</v>
       </c>
       <c r="D496">
-        <v>3.606431027150514E-08</v>
+        <v>3.606431177930772E-08</v>
       </c>
       <c r="E496">
         <v>0</v>
@@ -10791,10 +10791,10 @@
         </is>
       </c>
       <c r="C497">
-        <v>3.251728735084696E-07</v>
+        <v>3.251728757647232E-07</v>
       </c>
       <c r="D497">
-        <v>1.376705196198387E-07</v>
+        <v>1.376705193207622E-07</v>
       </c>
       <c r="E497">
         <v>0</v>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="C498">
-        <v>-1.51071523493035E-08</v>
+        <v>-1.5107152209759E-08</v>
       </c>
       <c r="D498">
-        <v>6.396011732050298E-09</v>
+        <v>6.396011614696162E-09</v>
       </c>
       <c r="E498">
         <v>0</v>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="C499">
-        <v>-1.654831370034717E-07</v>
+        <v>-1.654831384562128E-07</v>
       </c>
       <c r="D499">
-        <v>7.006165432491255E-08</v>
+        <v>7.006165430163457E-08</v>
       </c>
       <c r="E499">
         <v>0</v>
@@ -10854,10 +10854,10 @@
         </is>
       </c>
       <c r="C500">
-        <v>-1.480193586147419E-07</v>
+        <v>-1.48019359519358E-07</v>
       </c>
       <c r="D500">
-        <v>6.266790275098392E-08</v>
+        <v>6.266790256300749E-08</v>
       </c>
       <c r="E500">
         <v>0</v>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="C501">
-        <v>1.105953375032973E-06</v>
+        <v>1.105953377461555E-06</v>
       </c>
       <c r="D501">
-        <v>4.68234555279218E-07</v>
+        <v>4.682345520413206E-07</v>
       </c>
       <c r="E501">
         <v>0</v>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="C502">
-        <v>-4.923888343998062E-07</v>
+        <v>-4.923888356767048E-07</v>
       </c>
       <c r="D502">
-        <v>2.084658106791998E-07</v>
+        <v>2.084658093204691E-07</v>
       </c>
       <c r="E502">
         <v>0</v>
@@ -10917,10 +10917,10 @@
         </is>
       </c>
       <c r="C503">
-        <v>-6.216751332930777E-07</v>
+        <v>-6.216751343574023E-07</v>
       </c>
       <c r="D503">
-        <v>2.632025780986963E-07</v>
+        <v>2.632025761512582E-07</v>
       </c>
       <c r="E503">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="C504">
-        <v>-8.515144223516935E-07</v>
+        <v>-8.515144181708845E-07</v>
       </c>
       <c r="D504">
-        <v>3.60511108211771E-07</v>
+        <v>3.605111031570857E-07</v>
       </c>
       <c r="E504">
         <v>0</v>
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="C505">
-        <v>-4.167167149368548E-08</v>
+        <v>-4.167167225177515E-08</v>
       </c>
       <c r="D505">
-        <v>1.764280213802481E-08</v>
+        <v>1.764280229823788E-08</v>
       </c>
       <c r="E505">
         <v>0</v>
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="C506">
-        <v>4.201169266252726E-07</v>
+        <v>4.201169250539483E-07</v>
       </c>
       <c r="D506">
-        <v>1.77867590754259E-07</v>
+        <v>1.778675884684395E-07</v>
       </c>
       <c r="E506">
         <v>0</v>
@@ -11001,10 +11001,10 @@
         </is>
       </c>
       <c r="C507">
-        <v>4.863455938554515E-07</v>
+        <v>4.863455918685533E-07</v>
       </c>
       <c r="D507">
-        <v>2.059072452707377E-07</v>
+        <v>2.059072425535037E-07</v>
       </c>
       <c r="E507">
         <v>0</v>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="C508">
-        <v>0.03725753812140708</v>
+        <v>0.03725753150977917</v>
       </c>
       <c r="D508">
-        <v>0.0198444721863592</v>
+        <v>0.01984446865909624</v>
       </c>
       <c r="E508">
         <v>2</v>
@@ -11043,10 +11043,10 @@
         </is>
       </c>
       <c r="C509">
-        <v>0.04574729883809332</v>
+        <v>0.04574730558722508</v>
       </c>
       <c r="D509">
-        <v>0.02436637108000415</v>
+        <v>0.024366374667777</v>
       </c>
       <c r="E509">
         <v>2.4</v>
@@ -11064,10 +11064,10 @@
         </is>
       </c>
       <c r="C510">
-        <v>-0.7216396723419899</v>
+        <v>-0.7216396722477197</v>
       </c>
       <c r="D510">
-        <v>0.3843667383416248</v>
+        <v>0.3843667381807506</v>
       </c>
       <c r="E510">
         <v>38.4</v>
@@ -11085,10 +11085,10 @@
         </is>
       </c>
       <c r="C511">
-        <v>-0.01645160205185807</v>
+        <v>-0.01645159913239901</v>
       </c>
       <c r="D511">
-        <v>0.00876261223367213</v>
+        <v>0.008762610676158616</v>
       </c>
       <c r="E511">
         <v>0.9</v>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="C512">
-        <v>-0.02310766496856576</v>
+        <v>-0.02310766837765386</v>
       </c>
       <c r="D512">
-        <v>0.01230782917717624</v>
+        <v>0.01230783098941434</v>
       </c>
       <c r="E512">
         <v>1.2</v>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="C513">
-        <v>0.4610763986964394</v>
+        <v>0.461076398636207</v>
       </c>
       <c r="D513">
-        <v>0.2455829942360293</v>
+        <v>0.2455829941332419</v>
       </c>
       <c r="E513">
         <v>24.6</v>
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="C514">
-        <v>-0.02767557857766737</v>
+        <v>-0.02767557366643249</v>
       </c>
       <c r="D514">
-        <v>0.01474083573467138</v>
+        <v>0.01474083311455767</v>
       </c>
       <c r="E514">
         <v>1.5</v>
@@ -11169,10 +11169,10 @@
         </is>
       </c>
       <c r="C515">
-        <v>-0.03420153925577398</v>
+        <v>-0.03420154430155353</v>
       </c>
       <c r="D515">
-        <v>0.01821675635894771</v>
+        <v>0.01821675904123508</v>
       </c>
       <c r="E515">
         <v>1.8</v>
@@ -11190,10 +11190,10 @@
         </is>
       </c>
       <c r="C516">
-        <v>0.5103170544290697</v>
+        <v>0.5103170543624059</v>
       </c>
       <c r="D516">
-        <v>0.271810031028963</v>
+        <v>0.271810030915199</v>
       </c>
       <c r="E516">
         <v>27.2</v>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="C517">
-        <v>4.188348547780877E-07</v>
+        <v>4.188348526187533E-07</v>
       </c>
       <c r="D517">
-        <v>2.230838924256775E-07</v>
+        <v>2.230838912113237E-07</v>
       </c>
       <c r="E517">
         <v>0</v>
@@ -11232,10 +11232,10 @@
         </is>
       </c>
       <c r="C518">
-        <v>-1.92441397799686E-07</v>
+        <v>-1.92441396745964E-07</v>
       </c>
       <c r="D518">
-        <v>1.02500008285457E-07</v>
+        <v>1.025000076947026E-07</v>
       </c>
       <c r="E518">
         <v>0</v>
@@ -11253,10 +11253,10 @@
         </is>
       </c>
       <c r="C519">
-        <v>-2.201458270273464E-07</v>
+        <v>-2.201458258630981E-07</v>
       </c>
       <c r="D519">
-        <v>1.172562107338248E-07</v>
+        <v>1.172562100799523E-07</v>
       </c>
       <c r="E519">
         <v>0</v>
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="C520">
-        <v>-1.701375733895824E-07</v>
+        <v>-1.701375688502663E-07</v>
       </c>
       <c r="D520">
-        <v>9.062032848177639E-08</v>
+        <v>9.062032603791117E-08</v>
       </c>
       <c r="E520">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         </is>
       </c>
       <c r="C521">
-        <v>-1.608537380883222E-09</v>
+        <v>-1.608537658973064E-09</v>
       </c>
       <c r="D521">
-        <v>8.567548186259673E-10</v>
+        <v>8.567549664982139E-10</v>
       </c>
       <c r="E521">
         <v>0</v>
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="C522">
-        <v>1.028434551244663E-07</v>
+        <v>1.028434527391639E-07</v>
       </c>
       <c r="D522">
-        <v>5.477748095207412E-08</v>
+        <v>5.477747966582019E-08</v>
       </c>
       <c r="E522">
         <v>0</v>
@@ -11337,10 +11337,10 @@
         </is>
       </c>
       <c r="C523">
-        <v>6.979075420547938E-08</v>
+        <v>6.979075200912177E-08</v>
       </c>
       <c r="D523">
-        <v>3.717263003751474E-08</v>
+        <v>3.717262885696701E-08</v>
       </c>
       <c r="E523">
         <v>0</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="C524">
-        <v>9.833553773130857E-08</v>
+        <v>9.833555038654684E-08</v>
       </c>
       <c r="D524">
-        <v>5.237643016242134E-08</v>
+        <v>5.237643688789769E-08</v>
       </c>
       <c r="E524">
         <v>0</v>
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="C525">
-        <v>-2.430398868736617E-08</v>
+        <v>-2.43039943309542E-08</v>
       </c>
       <c r="D525">
-        <v>1.294502674740368E-08</v>
+        <v>1.29450297496194E-08</v>
       </c>
       <c r="E525">
         <v>0</v>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="C526">
-        <v>-7.970102552711026E-08</v>
+        <v>-7.970103298518549E-08</v>
       </c>
       <c r="D526">
-        <v>4.245113510031651E-08</v>
+        <v>4.245113906048693E-08</v>
       </c>
       <c r="E526">
         <v>0</v>
@@ -11421,10 +11421,10 @@
         </is>
       </c>
       <c r="C527">
-        <v>-5.791678100073562E-07</v>
+        <v>-5.791678204655412E-07</v>
       </c>
       <c r="D527">
-        <v>3.084819898586335E-07</v>
+        <v>3.084819953401586E-07</v>
       </c>
       <c r="E527">
         <v>0</v>
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="C528">
-        <v>4.703988231462544E-08</v>
+        <v>4.703988176063545E-08</v>
       </c>
       <c r="D528">
-        <v>2.505483945826909E-08</v>
+        <v>2.505483915598401E-08</v>
       </c>
       <c r="E528">
         <v>0</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="C529">
-        <v>2.524822565040166E-07</v>
+        <v>2.52482261201524E-07</v>
       </c>
       <c r="D529">
-        <v>1.344795541889107E-07</v>
+        <v>1.344795566522247E-07</v>
       </c>
       <c r="E529">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="C530">
-        <v>2.958270342135141E-07</v>
+        <v>2.958270399408547E-07</v>
       </c>
       <c r="D530">
-        <v>1.575662711071664E-07</v>
+        <v>1.575662741123532E-07</v>
       </c>
       <c r="E530">
         <v>0</v>
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5665208963708722</v>
+        <v>0.5665208963708723</v>
       </c>
     </row>
     <row r="3">
@@ -11532,7 +11532,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1340872020749305</v>
+        <v>0.1340872020749309</v>
       </c>
     </row>
     <row r="4">
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.09118688096449881</v>
+        <v>0.09118688096449838</v>
       </c>
     </row>
     <row r="5">
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.08542736897684611</v>
+        <v>0.08542736897684593</v>
       </c>
     </row>
     <row r="6">
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.04714770857992925</v>
+        <v>0.04714770857992927</v>
       </c>
     </row>
     <row r="7">
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.02863051935862939</v>
+        <v>0.02863051935862934</v>
       </c>
     </row>
     <row r="8">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.01387799268000329</v>
+        <v>0.01387799268000322</v>
       </c>
     </row>
     <row r="9">
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.009100162749135686</v>
+        <v>0.009100162749135662</v>
       </c>
     </row>
     <row r="10">
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.00629643855389874</v>
+        <v>0.00629643855389871</v>
       </c>
     </row>
     <row r="11">
@@ -11612,7 +11612,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.005758366583086073</v>
+        <v>0.005758366583086063</v>
       </c>
     </row>
     <row r="12">
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.002702379464889273</v>
+        <v>0.002702379464889275</v>
       </c>
     </row>
     <row r="14">
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.002138574603802997</v>
+        <v>0.002138574603802988</v>
       </c>
     </row>
     <row r="15">
@@ -11652,7 +11652,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.00172019512001334</v>
+        <v>0.001720195120013336</v>
       </c>
     </row>
     <row r="16">
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.001453112494549592</v>
+        <v>0.001453112494549587</v>
       </c>
     </row>
     <row r="17">
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.001036366245346938</v>
+        <v>0.001036366245346937</v>
       </c>
     </row>
     <row r="18">
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.641246367686858E-05</v>
+        <v>1.641246367686869E-05</v>
       </c>
     </row>
     <row r="19">
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>5.605910212737004E-06</v>
+        <v>5.605910212737118E-06</v>
       </c>
     </row>
     <row r="20">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>3.392073390431528E-06</v>
+        <v>3.392073390431407E-06</v>
       </c>
     </row>
     <row r="21">
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.552281837700786E-06</v>
+        <v>1.5522818377008E-06</v>
       </c>
     </row>
     <row r="22">
@@ -11722,7 +11722,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.136772641774826E-16</v>
+        <v>1.136772645621819E-16</v>
       </c>
     </row>
     <row r="23">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>9.12849117022797E-17</v>
+        <v>9.128491147706177E-17</v>
       </c>
     </row>
     <row r="24">
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>7.657649778042311E-17</v>
+        <v>7.657649805001322E-17</v>
       </c>
     </row>
   </sheetData>
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2351261304289207</v>
+        <v>0.2351261304289208</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2348736677440059</v>
+        <v>0.234873667744006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2327915016788113</v>
+        <v>0.2327915016788114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.2305650063878259</v>
+        <v>0.230565006387826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2268976465295912</v>
+        <v>0.2268976465295914</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.2213377954888254</v>
+        <v>0.2213377954888255</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3935018668737267</v>
+        <v>0.3935018668737266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.3182170713975063</v>
+        <v>0.3182170713975068</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2936727925108271</v>
+        <v>0.2936727925108273</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.2370396140579388</v>
+        <v>-0.2370396140579389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.2359955206627522</v>
+        <v>-0.2359955206627527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.2285038719485794</v>
+        <v>-0.2285038719485796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.2217901836143532</v>
+        <v>0.2217901836143535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.2077647244895507</v>
+        <v>-0.207764724489551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
